--- a/research/traditional_assets/database/data/pakistan/pakistan_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ22"/>
+  <dimension ref="A1:AQ20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08055000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="E2">
-        <v>0.05800000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="F2">
-        <v>0.1425</v>
+        <v>0.16</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,34 +603,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>3.484956601315584e-05</v>
+        <v>-9.675228286499451e-08</v>
       </c>
       <c r="J2">
-        <v>2.218683221297532e-05</v>
+        <v>-5.465082995306752e-08</v>
       </c>
       <c r="K2">
-        <v>1438.845</v>
+        <v>1192.27</v>
       </c>
       <c r="L2">
-        <v>0.2625423552531462</v>
+        <v>0.2250372775145807</v>
       </c>
       <c r="M2">
-        <v>699.066</v>
+        <v>445.347</v>
       </c>
       <c r="N2">
-        <v>0.08814348758038079</v>
+        <v>0.09955225215155918</v>
       </c>
       <c r="O2">
-        <v>0.4858521939472285</v>
+        <v>0.3735286470346482</v>
       </c>
       <c r="P2">
-        <v>699.066</v>
+        <v>445.347</v>
       </c>
       <c r="Q2">
-        <v>0.08814348758038079</v>
+        <v>0.09955225215155918</v>
       </c>
       <c r="R2">
-        <v>0.4858521939472285</v>
+        <v>0.3735286470346482</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,67 +639,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>7871.6</v>
+        <v>5589.57</v>
       </c>
       <c r="V2">
-        <v>0.9925104022191401</v>
+        <v>1.249484743489438</v>
       </c>
       <c r="W2">
-        <v>0.1333845912517707</v>
+        <v>0.1173201312097799</v>
       </c>
       <c r="X2">
-        <v>0.2702003691434616</v>
+        <v>0.5135158795865074</v>
       </c>
       <c r="Y2">
-        <v>-0.1368157778916909</v>
+        <v>-0.3961957483767274</v>
       </c>
       <c r="Z2">
-        <v>0.3134635522699665</v>
+        <v>0.1966180729313421</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.09581793850372697</v>
+        <v>0.1539397532465847</v>
       </c>
       <c r="AC2">
-        <v>-0.09514044646731451</v>
+        <v>-0.1539397532465847</v>
       </c>
       <c r="AD2">
-        <v>25481.004</v>
+        <v>25443.3</v>
       </c>
       <c r="AE2">
-        <v>0.2200469646726016</v>
+        <v>0.002563016349235137</v>
       </c>
       <c r="AF2">
-        <v>25481.22404696467</v>
+        <v>25443.30256301635</v>
       </c>
       <c r="AG2">
-        <v>17609.62404696467</v>
+        <v>19853.73256301635</v>
       </c>
       <c r="AH2">
-        <v>0.7626317844375735</v>
+        <v>0.8504686458194495</v>
       </c>
       <c r="AI2">
-        <v>0.7115866663538565</v>
+        <v>0.7595808701266747</v>
       </c>
       <c r="AJ2">
-        <v>0.6894750893550486</v>
+        <v>0.816111430331748</v>
       </c>
       <c r="AK2">
-        <v>0.6303238271847011</v>
+        <v>0.7114265431424556</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>108429.8042553191</v>
-      </c>
-      <c r="AP2">
-        <v>74934.57041261562</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apna Microfinance Bank Limited (KASE:AMBL)</t>
+          <t>Standard Chartered Bank (Pakistan) Limited (KASE:SCBPL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.191</v>
+        <v>0.17</v>
       </c>
       <c r="E3">
-        <v>-0.242</v>
+        <v>0.16</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,88 +725,91 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>-2.085448616139249e-06</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>-1.042724308069624e-06</v>
       </c>
       <c r="K3">
-        <v>0.065</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="L3">
-        <v>0.005371900826446281</v>
+        <v>0.3218063466232709</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>24.9</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.07351638618246235</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.3147914032869785</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>24.9</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.07351638618246235</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.3147914032869785</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>35</v>
+        <v>326.4</v>
       </c>
       <c r="V3">
-        <v>0.5756578947368421</v>
+        <v>0.9636846767050486</v>
       </c>
       <c r="W3">
-        <v>0.005241935483870968</v>
+        <v>0.1779527559055118</v>
       </c>
       <c r="X3">
-        <v>0.0767573957139268</v>
+        <v>0.1555066436381044</v>
       </c>
       <c r="Y3">
-        <v>-0.07151546023005582</v>
+        <v>0.02244611226740739</v>
       </c>
       <c r="Z3">
-        <v>-0.3246317709870415</v>
+        <v>1.008606544624277</v>
       </c>
       <c r="AA3">
-        <v>-0</v>
+        <v>-1.051698561357844e-06</v>
       </c>
       <c r="AB3">
-        <v>0.07675637966753736</v>
+        <v>0.1351696099708453</v>
       </c>
       <c r="AC3">
-        <v>-0.07675637966753736</v>
+        <v>-0.1351706616694066</v>
       </c>
       <c r="AD3">
-        <v>0.004</v>
+        <v>189</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>0.002563016349235137</v>
       </c>
       <c r="AF3">
-        <v>0.004</v>
+        <v>189.0025630163492</v>
       </c>
       <c r="AG3">
-        <v>-34.996</v>
+        <v>-137.3974369836507</v>
       </c>
       <c r="AH3">
-        <v>6.578514571409776e-05</v>
+        <v>0.358161161727186</v>
       </c>
       <c r="AI3">
-        <v>0.0002816108138552521</v>
+        <v>0.3447048687436348</v>
       </c>
       <c r="AJ3">
-        <v>-1.356223841264921</v>
+        <v>-0.6825419156361745</v>
       </c>
       <c r="AK3">
-        <v>1.682823619926909</v>
+        <v>-0.6191791348238174</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank (Pakistan) Limited (KASE:SCBPL)</t>
+          <t>BankIslami Pakistan Limited (KASE:BIPL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,10 +835,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0483</v>
+        <v>0.224</v>
       </c>
       <c r="E4">
-        <v>0.043</v>
+        <v>0.75</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,103 +847,94 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>3.729572267582013e-05</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>1.884992794683479e-05</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>65.3</v>
+        <v>13.7</v>
       </c>
       <c r="L4">
-        <v>0.3234274393263992</v>
+        <v>0.1802631578947368</v>
       </c>
       <c r="M4">
-        <v>62.3</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.07780691894592232</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.9540581929555896</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>62.3</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.07780691894592232</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.9540581929555896</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>313.1</v>
+        <v>112.8</v>
       </c>
       <c r="V4">
-        <v>0.3910328462595229</v>
+        <v>1.724770642201835</v>
       </c>
       <c r="W4">
-        <v>0.1373580143037442</v>
+        <v>0.1039453717754173</v>
       </c>
       <c r="X4">
-        <v>0.09125928684397293</v>
+        <v>0.1541502225567321</v>
       </c>
       <c r="Y4">
-        <v>0.0460987274597713</v>
+        <v>-0.05020485078131477</v>
       </c>
       <c r="Z4">
-        <v>1.222063605046212</v>
+        <v>2.275449101796407</v>
       </c>
       <c r="AA4">
-        <v>2.303581090157026e-05</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.08245165613860193</v>
+        <v>0.1367344547514456</v>
       </c>
       <c r="AC4">
-        <v>-0.08242862032770036</v>
+        <v>-0.1367344547514456</v>
       </c>
       <c r="AD4">
-        <v>265.3</v>
+        <v>35</v>
       </c>
       <c r="AE4">
-        <v>0.01234996795875958</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>265.3123499679588</v>
+        <v>35</v>
       </c>
       <c r="AG4">
-        <v>-47.78765003204126</v>
+        <v>-77.8</v>
       </c>
       <c r="AH4">
-        <v>0.248882998377958</v>
+        <v>0.348605577689243</v>
       </c>
       <c r="AI4">
-        <v>0.3737781541557217</v>
+        <v>0.2356902356902357</v>
       </c>
       <c r="AJ4">
-        <v>-0.06347040267578945</v>
+        <v>6.274193548387101</v>
       </c>
       <c r="AK4">
-        <v>-0.1204591942648141</v>
+        <v>-2.179271708683473</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>26530</v>
-      </c>
-      <c r="AP4">
-        <v>-4778.765003204126</v>
       </c>
     </row>
     <row r="5">
@@ -957,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Summit Bank Limited (KASE:SMBL)</t>
+          <t>MCB Bank Limited (KASE:MCB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -966,7 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.261</v>
+        <v>0.132</v>
+      </c>
+      <c r="E5">
+        <v>0.0444</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,100 +966,97 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.03258625233698607</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.03258625233698607</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>-17.9</v>
+        <v>126.7</v>
       </c>
       <c r="L5">
-        <v>-3.179396092362345</v>
+        <v>0.2532986805277889</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>94.2</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.1548832620848405</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>0.7434885556432518</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>94.2</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.1548832620848405</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>0.7434885556432518</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>43.8</v>
+        <v>345</v>
       </c>
       <c r="V5">
-        <v>1.186991869918699</v>
+        <v>0.5672476159158171</v>
       </c>
       <c r="W5">
-        <v>0.2801251956181534</v>
+        <v>0.120174523380442</v>
       </c>
       <c r="X5">
-        <v>0.253404669986823</v>
+        <v>0.2152851501763365</v>
       </c>
       <c r="Y5">
-        <v>0.02672052563133032</v>
+        <v>-0.09511062679589445</v>
       </c>
       <c r="Z5">
-        <v>0.4574373257241554</v>
+        <v>0.2492377619624908</v>
       </c>
       <c r="AA5">
-        <v>0.01490616812440342</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.09772694522341614</v>
+        <v>0.1441625972485297</v>
       </c>
       <c r="AC5">
-        <v>-0.08282077709901273</v>
+        <v>-0.1441625972485297</v>
       </c>
       <c r="AD5">
-        <v>148.7</v>
+        <v>952</v>
       </c>
       <c r="AE5">
-        <v>0.207696996713842</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>148.9076969967138</v>
+        <v>952</v>
       </c>
       <c r="AG5">
-        <v>105.1076969967138</v>
+        <v>607</v>
       </c>
       <c r="AH5">
-        <v>0.8014075810828621</v>
+        <v>0.6101781822843225</v>
       </c>
       <c r="AI5">
-        <v>2.059361633429996</v>
+        <v>0.5570509069631363</v>
       </c>
       <c r="AJ5">
-        <v>0.7401549297651528</v>
+        <v>0.499506254114549</v>
       </c>
       <c r="AK5">
-        <v>3.686993621716614</v>
+        <v>0.4450146627565982</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>660.8888888888888</v>
-      </c>
-      <c r="AP5">
-        <v>467.1453199853948</v>
       </c>
     </row>
     <row r="6">
@@ -1079,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Meezan Bank Limited (KASE:MEBL)</t>
+          <t>United Bank Limited (KASE:UBL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,13 +1076,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.248</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="E6">
-        <v>0.359</v>
+        <v>0.0117</v>
       </c>
       <c r="F6">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1109,28 +1097,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>139.8</v>
+        <v>118.8</v>
       </c>
       <c r="L6">
-        <v>0.3273238117536877</v>
+        <v>0.22762981414064</v>
       </c>
       <c r="M6">
-        <v>68.3</v>
+        <v>88</v>
       </c>
       <c r="N6">
-        <v>0.05521869189101786</v>
+        <v>0.1614975224811892</v>
       </c>
       <c r="O6">
-        <v>0.488555078683834</v>
+        <v>0.7407407407407408</v>
       </c>
       <c r="P6">
-        <v>68.3</v>
+        <v>88</v>
       </c>
       <c r="Q6">
-        <v>0.05521869189101786</v>
+        <v>0.1614975224811892</v>
       </c>
       <c r="R6">
-        <v>0.488555078683834</v>
+        <v>0.7407407407407408</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1139,55 +1127,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>876.6</v>
+        <v>594.9</v>
       </c>
       <c r="V6">
-        <v>0.7087072520009702</v>
+        <v>1.091759955955221</v>
       </c>
       <c r="W6">
-        <v>0.3119839321580005</v>
+        <v>0.1005416384563304</v>
       </c>
       <c r="X6">
-        <v>0.1093811644058421</v>
+        <v>0.2275797600601449</v>
       </c>
       <c r="Y6">
-        <v>0.2026027677521584</v>
+        <v>-0.1270381216038145</v>
       </c>
       <c r="Z6">
-        <v>1.970018450184501</v>
+        <v>0.2381582549968057</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.08652988329027866</v>
+        <v>0.1452020057309131</v>
       </c>
       <c r="AC6">
-        <v>-0.08652988329027866</v>
+        <v>-0.1452020057309131</v>
       </c>
       <c r="AD6">
-        <v>921.9</v>
+        <v>965.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>921.9</v>
+        <v>965.8</v>
       </c>
       <c r="AG6">
-        <v>45.29999999999995</v>
+        <v>370.9</v>
       </c>
       <c r="AH6">
-        <v>0.4270428015564202</v>
+        <v>0.6393062818560933</v>
       </c>
       <c r="AI6">
-        <v>0.6459048553212359</v>
+        <v>0.4967340431003446</v>
       </c>
       <c r="AJ6">
-        <v>0.03532990173139912</v>
+        <v>0.4050010919414719</v>
       </c>
       <c r="AK6">
-        <v>0.08225894316324671</v>
+        <v>0.274862902030532</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1204,7 +1192,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BankIslami Pakistan Limited (KASE:BIPL)</t>
+          <t>Meezan Bank Limited (KASE:MEBL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1213,10 +1201,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.109</v>
+        <v>0.331</v>
       </c>
       <c r="E7">
-        <v>0.331</v>
+        <v>0.424</v>
+      </c>
+      <c r="F7">
+        <v>0.3</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1231,82 +1222,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>10.2</v>
+        <v>162.4</v>
       </c>
       <c r="L7">
-        <v>0.148471615720524</v>
+        <v>0.3220305373785445</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>40.8</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.05184243964421855</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.251231527093596</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>40.8</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.05184243964421855</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.251231527093596</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>129.8</v>
+        <v>392.3</v>
       </c>
       <c r="V7">
-        <v>1.612422360248447</v>
+        <v>0.4984752223634054</v>
       </c>
       <c r="W7">
-        <v>0.08265802269043759</v>
+        <v>0.3265634425899859</v>
       </c>
       <c r="X7">
-        <v>0.1033456106316778</v>
+        <v>0.3002374088929327</v>
       </c>
       <c r="Y7">
-        <v>-0.02068758794124016</v>
+        <v>0.02632603369705327</v>
       </c>
       <c r="Z7">
-        <v>-0.5358814352574104</v>
+        <v>0.9294139329155916</v>
       </c>
       <c r="AA7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.0866439143113631</v>
+        <v>0.149144631459666</v>
       </c>
       <c r="AC7">
-        <v>-0.0866439143113631</v>
+        <v>-0.149144631459666</v>
       </c>
       <c r="AD7">
-        <v>48.9</v>
+        <v>2358.4</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>48.9</v>
+        <v>2358.4</v>
       </c>
       <c r="AG7">
-        <v>-80.90000000000001</v>
+        <v>1966.1</v>
       </c>
       <c r="AH7">
-        <v>0.3778979907264297</v>
+        <v>0.7497933490176131</v>
       </c>
       <c r="AI7">
-        <v>0.2706142778085224</v>
+        <v>0.838452787258248</v>
       </c>
       <c r="AJ7">
-        <v>202.2499999999971</v>
+        <v>0.7141404235225745</v>
       </c>
       <c r="AK7">
-        <v>-1.589390962671906</v>
+        <v>0.8122701921090685</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1323,7 +1317,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MCB Bank Limited (KASE:MCB)</t>
+          <t>Allied Bank Limited (KASE:ABL)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1332,10 +1326,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0762</v>
+        <v>0.136</v>
       </c>
       <c r="E8">
-        <v>0.0481</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1350,28 +1344,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>169.2</v>
+        <v>74.2</v>
       </c>
       <c r="L8">
-        <v>0.3235181644359464</v>
+        <v>0.2158231529959279</v>
       </c>
       <c r="M8">
-        <v>168.8</v>
+        <v>40</v>
       </c>
       <c r="N8">
-        <v>0.1638516792855756</v>
+        <v>0.1236093943139678</v>
       </c>
       <c r="O8">
-        <v>0.9976359338061467</v>
+        <v>0.5390835579514824</v>
       </c>
       <c r="P8">
-        <v>168.8</v>
+        <v>40</v>
       </c>
       <c r="Q8">
-        <v>0.1638516792855756</v>
+        <v>0.1236093943139678</v>
       </c>
       <c r="R8">
-        <v>0.9976359338061467</v>
+        <v>0.5390835579514824</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1380,55 +1374,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>321.7</v>
+        <v>228.2</v>
       </c>
       <c r="V8">
-        <v>0.3122694622403416</v>
+        <v>0.7051915945611865</v>
       </c>
       <c r="W8">
-        <v>0.149641814804988</v>
+        <v>0.09618874773139746</v>
       </c>
       <c r="X8">
-        <v>0.1309226341118389</v>
+        <v>0.3794237617761525</v>
       </c>
       <c r="Y8">
-        <v>0.01871918069314918</v>
+        <v>-0.283235014044755</v>
       </c>
       <c r="Z8">
-        <v>0.3030469838712948</v>
+        <v>0.112773076166109</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.08941448976393665</v>
+        <v>0.1513792850600506</v>
       </c>
       <c r="AC8">
-        <v>-0.08941448976393665</v>
+        <v>-0.1513792850600506</v>
       </c>
       <c r="AD8">
-        <v>1274.8</v>
+        <v>1401.5</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>1274.8</v>
+        <v>1401.5</v>
       </c>
       <c r="AG8">
-        <v>953.0999999999999</v>
+        <v>1173.3</v>
       </c>
       <c r="AH8">
-        <v>0.553058568329718</v>
+        <v>0.8124166714973046</v>
       </c>
       <c r="AI8">
-        <v>0.5462102060928061</v>
+        <v>0.7158910966951014</v>
       </c>
       <c r="AJ8">
-        <v>0.4805626985327484</v>
+        <v>0.7838198944485268</v>
       </c>
       <c r="AK8">
-        <v>0.4736606699135275</v>
+        <v>0.6784041630529054</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1445,7 +1439,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Habib Bank Limited (KASE:HBL)</t>
+          <t>Faysal Bank Limited (KASE:FABL)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1454,13 +1448,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.06610000000000001</v>
+        <v>0.176</v>
       </c>
       <c r="E9">
-        <v>-0.0154</v>
-      </c>
-      <c r="F9">
-        <v>0.135</v>
+        <v>0.179</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1475,28 +1466,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>190</v>
+        <v>43.6</v>
       </c>
       <c r="L9">
-        <v>0.2138917032534054</v>
+        <v>0.2259067357512954</v>
       </c>
       <c r="M9">
-        <v>48.7</v>
+        <v>4.8</v>
       </c>
       <c r="N9">
-        <v>0.05021653949267891</v>
+        <v>0.02771362586605081</v>
       </c>
       <c r="O9">
-        <v>0.2563157894736842</v>
+        <v>0.110091743119266</v>
       </c>
       <c r="P9">
-        <v>48.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q9">
-        <v>0.05021653949267891</v>
+        <v>0.02771362586605081</v>
       </c>
       <c r="R9">
-        <v>0.2563157894736842</v>
+        <v>0.110091743119266</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1505,55 +1496,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>1523.4</v>
+        <v>142.1</v>
       </c>
       <c r="V9">
-        <v>1.570839348319241</v>
+        <v>0.8204387990762125</v>
       </c>
       <c r="W9">
-        <v>0.1244514311914587</v>
+        <v>0.1144657390391179</v>
       </c>
       <c r="X9">
-        <v>0.1933636888675405</v>
+        <v>0.4156347141306339</v>
       </c>
       <c r="Y9">
-        <v>-0.06891225767608182</v>
+        <v>-0.301168975091516</v>
       </c>
       <c r="Z9">
-        <v>0.3657512249351504</v>
+        <v>0.210233239073318</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.09339759535965919</v>
+        <v>0.1520667229734882</v>
       </c>
       <c r="AC9">
-        <v>-0.09339759535965919</v>
+        <v>-0.1520667229734882</v>
       </c>
       <c r="AD9">
-        <v>2583.4</v>
+        <v>855.8</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>2583.4</v>
+        <v>855.8</v>
       </c>
       <c r="AG9">
-        <v>1060</v>
+        <v>713.6999999999999</v>
       </c>
       <c r="AH9">
-        <v>0.7270629291905888</v>
+        <v>0.8316812439261418</v>
       </c>
       <c r="AI9">
-        <v>0.6103000236239075</v>
+        <v>0.7355393210141813</v>
       </c>
       <c r="AJ9">
-        <v>0.5222189378263868</v>
+        <v>0.8047130454391702</v>
       </c>
       <c r="AK9">
-        <v>0.3912016533805728</v>
+        <v>0.6987468180928138</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1570,7 +1561,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>United Bank Limited (KASE:UBL)</t>
+          <t>Bank AL Habib Limited (KASE:BAHL)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1579,10 +1570,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0281</v>
+        <v>0.211</v>
       </c>
       <c r="E10">
-        <v>-0.00601</v>
+        <v>0.169</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1597,28 +1588,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>158.4</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="L10">
-        <v>0.2869045462778482</v>
+        <v>0.2256788821513314</v>
       </c>
       <c r="M10">
-        <v>110.7</v>
+        <v>33.7</v>
       </c>
       <c r="N10">
-        <v>0.1167967925722726</v>
+        <v>0.1241709653647753</v>
       </c>
       <c r="O10">
-        <v>0.6988636363636364</v>
+        <v>0.3936915887850468</v>
       </c>
       <c r="P10">
-        <v>110.7</v>
+        <v>33.7</v>
       </c>
       <c r="Q10">
-        <v>0.1167967925722726</v>
+        <v>0.1241709653647753</v>
       </c>
       <c r="R10">
-        <v>0.6988636363636364</v>
+        <v>0.3936915887850468</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1627,55 +1618,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>1562.9</v>
+        <v>160.8</v>
       </c>
       <c r="V10">
-        <v>1.648976577336991</v>
+        <v>0.5924834193072956</v>
       </c>
       <c r="W10">
-        <v>0.1351535836177475</v>
+        <v>0.1651871864145117</v>
       </c>
       <c r="X10">
-        <v>0.1955761940911969</v>
+        <v>0.5071899010079906</v>
       </c>
       <c r="Y10">
-        <v>-0.06042261047344949</v>
+        <v>-0.3420027145934788</v>
       </c>
       <c r="Z10">
-        <v>0.7187866163259994</v>
+        <v>0.1555209315675099</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.09348261076584984</v>
+        <v>0.1533048374068057</v>
       </c>
       <c r="AC10">
-        <v>-0.09348261076584984</v>
+        <v>-0.1533048374068057</v>
       </c>
       <c r="AD10">
-        <v>2572.7</v>
+        <v>1759.7</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>2572.7</v>
+        <v>1759.7</v>
       </c>
       <c r="AG10">
-        <v>1009.8</v>
+        <v>1598.9</v>
       </c>
       <c r="AH10">
-        <v>0.7307768782843346</v>
+        <v>0.8663778248239871</v>
       </c>
       <c r="AI10">
-        <v>0.676741372053872</v>
+        <v>0.8134331807886099</v>
       </c>
       <c r="AJ10">
-        <v>0.5158357172047404</v>
+        <v>0.8548895899053628</v>
       </c>
       <c r="AK10">
-        <v>0.4510653504265868</v>
+        <v>0.7984519350811486</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1692,7 +1683,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Faysal Bank Limited (KASE:FABL)</t>
+          <t>Habib Bank Limited (KASE:HBL)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1701,10 +1692,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.122</v>
+        <v>0.103</v>
       </c>
       <c r="E11">
-        <v>0.0983</v>
+        <v>0.267</v>
+      </c>
+      <c r="F11">
+        <v>0.15</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1719,28 +1713,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>43.2</v>
+        <v>138.8</v>
       </c>
       <c r="L11">
-        <v>0.2254697286012526</v>
+        <v>0.1666866818782275</v>
       </c>
       <c r="M11">
-        <v>4.03</v>
+        <v>43.6</v>
       </c>
       <c r="N11">
-        <v>0.02036382011116726</v>
+        <v>0.1055690072639225</v>
       </c>
       <c r="O11">
-        <v>0.09328703703703704</v>
+        <v>0.3141210374639769</v>
       </c>
       <c r="P11">
-        <v>4.03</v>
+        <v>43.6</v>
       </c>
       <c r="Q11">
-        <v>0.02036382011116726</v>
+        <v>0.1055690072639225</v>
       </c>
       <c r="R11">
-        <v>0.09328703703703704</v>
+        <v>0.3141210374639769</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1749,55 +1743,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>137.7</v>
+        <v>1412.2</v>
       </c>
       <c r="V11">
-        <v>0.6958059626073774</v>
+        <v>3.419370460048426</v>
       </c>
       <c r="W11">
-        <v>0.1204684885666481</v>
+        <v>0.08530514412144306</v>
       </c>
       <c r="X11">
-        <v>0.2261724746156208</v>
+        <v>0.5221484635662537</v>
       </c>
       <c r="Y11">
-        <v>-0.1057039860489727</v>
+        <v>-0.4368433194448106</v>
       </c>
       <c r="Z11">
-        <v>0.2889632914065092</v>
+        <v>0.3098879833277511</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.0944586157687855</v>
+        <v>0.1534601933830667</v>
       </c>
       <c r="AC11">
-        <v>-0.0944586157687855</v>
+        <v>-0.1534601933830667</v>
       </c>
       <c r="AD11">
-        <v>675.5</v>
+        <v>2781.9</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>675.5</v>
+        <v>2781.9</v>
       </c>
       <c r="AG11">
-        <v>537.8</v>
+        <v>1369.7</v>
       </c>
       <c r="AH11">
-        <v>0.7734142431875429</v>
+        <v>0.8707314782935304</v>
       </c>
       <c r="AI11">
-        <v>0.6394358197652403</v>
+        <v>0.6929112284547175</v>
       </c>
       <c r="AJ11">
-        <v>0.7310044855239908</v>
+        <v>0.7683289392494531</v>
       </c>
       <c r="AK11">
-        <v>0.5853924023076086</v>
+        <v>0.5262814108967955</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1814,7 +1808,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Askari Bank Limited (KASE:AKBL)</t>
+          <t>Habib Metropolitan Bank Limited (KASE:HMB)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1823,10 +1817,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.112</v>
+        <v>0.187</v>
       </c>
       <c r="E12">
-        <v>0.127</v>
+        <v>0.199</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1841,28 +1835,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>55.4</v>
+        <v>60.9</v>
       </c>
       <c r="L12">
-        <v>0.2557710064635272</v>
+        <v>0.2923667786845895</v>
       </c>
       <c r="M12">
-        <v>21.9</v>
+        <v>25.6</v>
       </c>
       <c r="N12">
-        <v>0.1392244119516847</v>
+        <v>0.1628498727735369</v>
       </c>
       <c r="O12">
-        <v>0.3953068592057762</v>
+        <v>0.4203612479474549</v>
       </c>
       <c r="P12">
-        <v>21.9</v>
+        <v>25.6</v>
       </c>
       <c r="Q12">
-        <v>0.1392244119516847</v>
+        <v>0.1628498727735369</v>
       </c>
       <c r="R12">
-        <v>0.3953068592057762</v>
+        <v>0.4203612479474549</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1871,55 +1865,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>225.1</v>
+        <v>242.8</v>
       </c>
       <c r="V12">
-        <v>1.431023521932613</v>
+        <v>1.544529262086514</v>
       </c>
       <c r="W12">
-        <v>0.1798701298701299</v>
+        <v>0.1703496503496504</v>
       </c>
       <c r="X12">
-        <v>0.2308147660336853</v>
+        <v>0.6426670326298241</v>
       </c>
       <c r="Y12">
-        <v>-0.05094463616355543</v>
+        <v>-0.4723173822801737</v>
       </c>
       <c r="Z12">
-        <v>0.2691686342736423</v>
+        <v>0.1154656319290466</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.09458032504003508</v>
+        <v>0.1544193131101026</v>
       </c>
       <c r="AC12">
-        <v>-0.09458032504003508</v>
+        <v>-0.1544193131101026</v>
       </c>
       <c r="AD12">
-        <v>553.6</v>
+        <v>1378.1</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>553.6</v>
+        <v>1378.1</v>
       </c>
       <c r="AG12">
-        <v>328.5</v>
+        <v>1135.3</v>
       </c>
       <c r="AH12">
-        <v>0.7787311858207905</v>
+        <v>0.897609587702729</v>
       </c>
       <c r="AI12">
-        <v>0.6278067589022455</v>
+        <v>0.8035568513119533</v>
       </c>
       <c r="AJ12">
-        <v>0.6762041992589543</v>
+        <v>0.8783752417794971</v>
       </c>
       <c r="AK12">
-        <v>0.5002284148012791</v>
+        <v>0.7711588099443011</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1936,7 +1930,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Allied Bank Limited (KASE:ABL)</t>
+          <t>The Bank of Punjab (KASE:BOP)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1945,10 +1939,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.07200000000000001</v>
+        <v>0.209</v>
       </c>
       <c r="E13">
-        <v>0.0388</v>
+        <v>0.226</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1963,28 +1957,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>111.1</v>
+        <v>49</v>
       </c>
       <c r="L13">
-        <v>0.2973768736616702</v>
+        <v>0.2494908350305499</v>
       </c>
       <c r="M13">
-        <v>66.90000000000001</v>
+        <v>14.871</v>
       </c>
       <c r="N13">
-        <v>0.1252808988764045</v>
+        <v>0.24785</v>
       </c>
       <c r="O13">
-        <v>0.6021602160216022</v>
+        <v>0.3034897959183673</v>
       </c>
       <c r="P13">
-        <v>66.90000000000001</v>
+        <v>14.871</v>
       </c>
       <c r="Q13">
-        <v>0.1252808988764045</v>
+        <v>0.24785</v>
       </c>
       <c r="R13">
-        <v>0.6021602160216022</v>
+        <v>0.3034897959183673</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1993,55 +1987,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>287.5</v>
+        <v>135.5</v>
       </c>
       <c r="V13">
-        <v>0.5383895131086143</v>
+        <v>2.258333333333333</v>
       </c>
       <c r="W13">
-        <v>0.1483905436089221</v>
+        <v>0.1574550128534704</v>
       </c>
       <c r="X13">
-        <v>0.2869960683001001</v>
+        <v>0.7381262214407531</v>
       </c>
       <c r="Y13">
-        <v>-0.138605524691178</v>
+        <v>-0.5806712085872827</v>
       </c>
       <c r="Z13">
-        <v>0.2530479544838797</v>
+        <v>0.2156346069389548</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.09570056789459394</v>
+        <v>0.1549359583220422</v>
       </c>
       <c r="AC13">
-        <v>-0.09570056789459394</v>
+        <v>-0.1549359583220422</v>
       </c>
       <c r="AD13">
-        <v>2564.7</v>
+        <v>622.5</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>2564.7</v>
+        <v>622.5</v>
       </c>
       <c r="AG13">
-        <v>2277.2</v>
+        <v>487</v>
       </c>
       <c r="AH13">
-        <v>0.827669667925259</v>
+        <v>0.9120879120879121</v>
       </c>
       <c r="AI13">
-        <v>0.7687719193069752</v>
+        <v>0.6880733944954128</v>
       </c>
       <c r="AJ13">
-        <v>0.810045532157086</v>
+        <v>0.8903107861060329</v>
       </c>
       <c r="AK13">
-        <v>0.7469658203765662</v>
+        <v>0.6331253250130005</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2058,7 +2052,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bank AL Habib Limited (KASE:BAHL)</t>
+          <t>Bank Alfalah Limited (KASE:BAFL)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2067,10 +2061,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.176</v>
+        <v>0.152</v>
       </c>
       <c r="E14">
-        <v>0.2</v>
+        <v>0.154</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2085,28 +2079,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>110</v>
+        <v>78.8</v>
       </c>
       <c r="L14">
-        <v>0.2792586951002793</v>
+        <v>0.2247575584711922</v>
       </c>
       <c r="M14">
-        <v>28.9</v>
+        <v>25</v>
       </c>
       <c r="N14">
-        <v>0.06646734130634774</v>
+        <v>0.1056635672020287</v>
       </c>
       <c r="O14">
-        <v>0.2627272727272727</v>
+        <v>0.317258883248731</v>
       </c>
       <c r="P14">
-        <v>28.9</v>
+        <v>25</v>
       </c>
       <c r="Q14">
-        <v>0.06646734130634774</v>
+        <v>0.1056635672020287</v>
       </c>
       <c r="R14">
-        <v>0.2627272727272727</v>
+        <v>0.317258883248731</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2115,55 +2109,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>327.2</v>
+        <v>176.3</v>
       </c>
       <c r="V14">
-        <v>0.7525298988040477</v>
+        <v>0.7451394759087068</v>
       </c>
       <c r="W14">
-        <v>0.2363558229480017</v>
+        <v>0.1425728243169893</v>
       </c>
       <c r="X14">
-        <v>0.3030681360978402</v>
+        <v>0.7441149683980643</v>
       </c>
       <c r="Y14">
-        <v>-0.0667123131498385</v>
+        <v>-0.6015421440810751</v>
       </c>
       <c r="Z14">
-        <v>0.1991862641880391</v>
+        <v>0.1403017327624155</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.09593530911286</v>
+        <v>0.1549635427674074</v>
       </c>
       <c r="AC14">
-        <v>-0.09593530911286</v>
+        <v>-0.1549635427674074</v>
       </c>
       <c r="AD14">
-        <v>2247.9</v>
+        <v>2478.6</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>2247.9</v>
+        <v>2478.6</v>
       </c>
       <c r="AG14">
-        <v>1920.7</v>
+        <v>2302.3</v>
       </c>
       <c r="AH14">
-        <v>0.837924479069594</v>
+        <v>0.9128609310548026</v>
       </c>
       <c r="AI14">
-        <v>0.8124254580938957</v>
+        <v>0.8431472599244821</v>
       </c>
       <c r="AJ14">
-        <v>0.8154107408193589</v>
+        <v>0.9068100358422939</v>
       </c>
       <c r="AK14">
-        <v>0.7872689265073576</v>
+        <v>0.8331403343707028</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2180,7 +2174,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bank Alfalah Limited (KASE:BAFL)</t>
+          <t>Askari Bank Limited (KASE:AKBL)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2189,10 +2183,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.08699999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="E15">
-        <v>0.101</v>
+        <v>0.218</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2207,28 +2201,28 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>75.59999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="L15">
-        <v>0.2281919710232418</v>
+        <v>0.2861244019138756</v>
       </c>
       <c r="M15">
-        <v>48.6</v>
+        <v>0.042</v>
       </c>
       <c r="N15">
-        <v>0.1394148020654045</v>
+        <v>0.0003753351206434316</v>
       </c>
       <c r="O15">
-        <v>0.6428571428571429</v>
+        <v>0.0007023411371237459</v>
       </c>
       <c r="P15">
-        <v>48.6</v>
+        <v>0.042</v>
       </c>
       <c r="Q15">
-        <v>0.1394148020654045</v>
+        <v>0.0003753351206434316</v>
       </c>
       <c r="R15">
-        <v>0.6428571428571429</v>
+        <v>0.0007023411371237459</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2237,55 +2231,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>163.6</v>
+        <v>180.4</v>
       </c>
       <c r="V15">
-        <v>0.4693057946069994</v>
+        <v>1.612153708668454</v>
       </c>
       <c r="W15">
-        <v>0.1316155988857939</v>
+        <v>0.182205971968312</v>
       </c>
       <c r="X15">
-        <v>0.3416881795319886</v>
+        <v>0.8979459606343869</v>
       </c>
       <c r="Y15">
-        <v>-0.2100725806461947</v>
+        <v>-0.7157399886660749</v>
       </c>
       <c r="Z15">
-        <v>0.1664573179922625</v>
+        <v>0.3182579564489113</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.09639944320180591</v>
+        <v>0.1555364624175127</v>
       </c>
       <c r="AC15">
-        <v>-0.09639944320180591</v>
+        <v>-0.1555364624175127</v>
       </c>
       <c r="AD15">
-        <v>2109.8</v>
+        <v>1462.3</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>2109.8</v>
+        <v>1462.3</v>
       </c>
       <c r="AG15">
-        <v>1946.2</v>
+        <v>1281.9</v>
       </c>
       <c r="AH15">
-        <v>0.8582004555808657</v>
+        <v>0.9289162749332994</v>
       </c>
       <c r="AI15">
-        <v>0.7922048663262241</v>
+        <v>0.8322235501678903</v>
       </c>
       <c r="AJ15">
-        <v>0.8480913369356807</v>
+        <v>0.9197158846319414</v>
       </c>
       <c r="AK15">
-        <v>0.7786045767322771</v>
+        <v>0.8130272087270882</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2302,7 +2296,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Bank of Punjab (KASE:BOP)</t>
+          <t>National Bank of Pakistan (KASE:NBP)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2311,10 +2305,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.168</v>
+        <v>0.0906</v>
       </c>
       <c r="E16">
-        <v>0.142</v>
+        <v>-0.007189999999999999</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2329,28 +2323,28 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>56.9</v>
+        <v>101.9</v>
       </c>
       <c r="L16">
-        <v>0.2793323514973</v>
+        <v>0.1660691003911343</v>
       </c>
       <c r="M16">
-        <v>15.5</v>
+        <v>0.004</v>
       </c>
       <c r="N16">
-        <v>0.1221434200157604</v>
+        <v>1.804239963915201e-05</v>
       </c>
       <c r="O16">
-        <v>0.2724077328646749</v>
+        <v>3.925417075564279e-05</v>
       </c>
       <c r="P16">
-        <v>15.5</v>
+        <v>0.004</v>
       </c>
       <c r="Q16">
-        <v>0.1221434200157604</v>
+        <v>1.804239963915201e-05</v>
       </c>
       <c r="R16">
-        <v>0.2724077328646749</v>
+        <v>3.925417075564279e-05</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2359,55 +2353,55 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>234.5</v>
+        <v>997.1</v>
       </c>
       <c r="V16">
-        <v>1.847911741528763</v>
+        <v>4.497519170049617</v>
       </c>
       <c r="W16">
-        <v>0.1852213541666667</v>
+        <v>0.05858341956996665</v>
       </c>
       <c r="X16">
-        <v>0.3644809338909881</v>
+        <v>1.983464022605</v>
       </c>
       <c r="Y16">
-        <v>-0.1792595797243214</v>
+        <v>-1.924880603035034</v>
       </c>
       <c r="Z16">
-        <v>0.1753012048192771</v>
+        <v>0.1189608375339279</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.09662261963242534</v>
+        <v>0.1569702485975942</v>
       </c>
       <c r="AC16">
-        <v>-0.09662261963242534</v>
+        <v>-0.1569702485975942</v>
       </c>
       <c r="AD16">
-        <v>834.1</v>
+        <v>6952.2</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>834.1</v>
+        <v>6952.2</v>
       </c>
       <c r="AG16">
-        <v>599.6</v>
+        <v>5955.099999999999</v>
       </c>
       <c r="AH16">
-        <v>0.8679500520291363</v>
+        <v>0.9690963074478317</v>
       </c>
       <c r="AI16">
-        <v>0.7261251849917297</v>
+        <v>0.8367676086851861</v>
       </c>
       <c r="AJ16">
-        <v>0.8253269098417069</v>
+        <v>0.9641076285455252</v>
       </c>
       <c r="AK16">
-        <v>0.6558739881863924</v>
+        <v>0.8145063121469506</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2424,7 +2418,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Habib Metropolitan Bank Limited (KASE:HMB)</t>
+          <t>The Bank of Khyber (KASE:BOK)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2433,10 +2427,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.158</v>
+        <v>0.0147</v>
       </c>
       <c r="E17">
-        <v>0.201</v>
+        <v>-0.207</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2451,85 +2445,82 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>80.3</v>
+        <v>2.65</v>
       </c>
       <c r="L17">
-        <v>0.3528119507908611</v>
+        <v>0.08466453674121405</v>
       </c>
       <c r="M17">
-        <v>33.2</v>
+        <v>-0</v>
       </c>
       <c r="N17">
-        <v>0.130503144654088</v>
+        <v>-0</v>
       </c>
       <c r="O17">
-        <v>0.4134495641344957</v>
+        <v>-0</v>
       </c>
       <c r="P17">
-        <v>33.2</v>
+        <v>-0</v>
       </c>
       <c r="Q17">
-        <v>0.130503144654088</v>
+        <v>-0</v>
       </c>
       <c r="R17">
-        <v>0.4134495641344957</v>
+        <v>-0</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
       <c r="U17">
-        <v>288</v>
+        <v>52.9</v>
       </c>
       <c r="V17">
-        <v>1.132075471698113</v>
+        <v>0.8357030015797788</v>
       </c>
       <c r="W17">
-        <v>0.2291666666666667</v>
+        <v>0.02717948717948718</v>
       </c>
       <c r="X17">
-        <v>0.3752106004450495</v>
+        <v>0.4292555680592771</v>
       </c>
       <c r="Y17">
-        <v>-0.1460439337783828</v>
+        <v>-0.40207608087979</v>
       </c>
       <c r="Z17">
-        <v>0.1858110866193158</v>
+        <v>0.06795484151107251</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.09671738880015204</v>
+        <v>0.1591319122189949</v>
       </c>
       <c r="AC17">
-        <v>-0.09671738880015204</v>
+        <v>-0.1591319122189949</v>
       </c>
       <c r="AD17">
-        <v>1734.5</v>
+        <v>327.3</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>1734.5</v>
+        <v>327.3</v>
       </c>
       <c r="AG17">
-        <v>1446.5</v>
+        <v>274.4</v>
       </c>
       <c r="AH17">
-        <v>0.872090100055307</v>
+        <v>0.8379416282642089</v>
       </c>
       <c r="AI17">
-        <v>0.8206377744133233</v>
+        <v>0.81825</v>
       </c>
       <c r="AJ17">
-        <v>0.8504321241695573</v>
+        <v>0.8125555226532425</v>
       </c>
       <c r="AK17">
-        <v>0.7923422436459246</v>
+        <v>0.7905502736963411</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2546,7 +2537,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Soneri Bank Limited (KASE:SNBL)</t>
+          <t>Summit Bank Limited (KASE:SMBL)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2554,104 +2545,80 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D18">
-        <v>0.0849</v>
-      </c>
-      <c r="E18">
-        <v>0.06370000000000001</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
       <c r="K18">
-        <v>17.3</v>
-      </c>
-      <c r="L18">
-        <v>0.1970387243735763</v>
+        <v>-14.5</v>
       </c>
       <c r="M18">
-        <v>8.08</v>
+        <v>-0</v>
       </c>
       <c r="N18">
-        <v>0.1346666666666667</v>
+        <v>-0</v>
       </c>
       <c r="O18">
-        <v>0.4670520231213873</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>8.08</v>
+        <v>-0</v>
       </c>
       <c r="Q18">
-        <v>0.1346666666666667</v>
+        <v>-0</v>
       </c>
       <c r="R18">
-        <v>0.4670520231213873</v>
+        <v>0</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
       <c r="U18">
-        <v>71.59999999999999</v>
+        <v>30.6</v>
       </c>
       <c r="V18">
-        <v>1.193333333333333</v>
+        <v>1.545454545454545</v>
       </c>
       <c r="W18">
-        <v>0.1310606060606061</v>
+        <v>0.1892950391644909</v>
       </c>
       <c r="X18">
-        <v>0.530041598679406</v>
+        <v>0.5198418581650242</v>
       </c>
       <c r="Y18">
-        <v>-0.3989809926187999</v>
+        <v>-0.3305468190005333</v>
       </c>
       <c r="Z18">
-        <v>0.1161529302817833</v>
+        <v>0</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.09762942774157043</v>
+        <v>0.1605410939579424</v>
       </c>
       <c r="AC18">
-        <v>-0.09762942774157043</v>
+        <v>-0.1605410939579424</v>
       </c>
       <c r="AD18">
-        <v>621.3</v>
+        <v>132.6</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>621.3</v>
+        <v>132.6</v>
       </c>
       <c r="AG18">
-        <v>549.6999999999999</v>
+        <v>102</v>
       </c>
       <c r="AH18">
-        <v>0.9119330691325407</v>
+        <v>0.8700787401574802</v>
       </c>
       <c r="AI18">
-        <v>0.8231319554848967</v>
+        <v>2.213689482470785</v>
       </c>
       <c r="AJ18">
-        <v>0.9015909463670657</v>
+        <v>0.8374384236453202</v>
       </c>
       <c r="AK18">
-        <v>0.804596018735363</v>
+        <v>3.48122866894198</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2668,7 +2635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>National Bank of Pakistan (KASE:NBP)</t>
+          <t>Soneri Bank Limited (KASE:SNBL)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2677,10 +2644,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.0634</v>
+        <v>0.111</v>
       </c>
       <c r="E19">
-        <v>0.05230000000000001</v>
+        <v>0.0269</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2695,28 +2662,28 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>169.4</v>
+        <v>7.84</v>
       </c>
       <c r="L19">
-        <v>0.2529113168109884</v>
+        <v>0.1121602288984263</v>
       </c>
       <c r="M19">
-        <v>0.016</v>
+        <v>7.24</v>
       </c>
       <c r="N19">
-        <v>3.843382176315157e-05</v>
+        <v>0.1486652977412731</v>
       </c>
       <c r="O19">
-        <v>9.445100354191263e-05</v>
+        <v>0.9234693877551021</v>
       </c>
       <c r="P19">
-        <v>0.016</v>
+        <v>7.24</v>
       </c>
       <c r="Q19">
-        <v>3.843382176315157e-05</v>
+        <v>0.1486652977412731</v>
       </c>
       <c r="R19">
-        <v>9.445100354191263e-05</v>
+        <v>0.9234693877551021</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2725,55 +2692,55 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>1208.8</v>
+        <v>50.9</v>
       </c>
       <c r="V19">
-        <v>2.903675234206101</v>
+        <v>1.04517453798768</v>
       </c>
       <c r="W19">
-        <v>0.1028224582701062</v>
+        <v>0.05872659176029962</v>
       </c>
       <c r="X19">
-        <v>0.5636810881760551</v>
+        <v>0.5986366984167468</v>
       </c>
       <c r="Y19">
-        <v>-0.4608586299059489</v>
+        <v>-0.5399101066564472</v>
       </c>
       <c r="Z19">
-        <v>0.6556317968696469</v>
+        <v>0.1023126463700234</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.09775721095678296</v>
+        <v>0.1613792037658644</v>
       </c>
       <c r="AC19">
-        <v>-0.09775721095678296</v>
+        <v>-0.1613792037658644</v>
       </c>
       <c r="AD19">
-        <v>4630.7</v>
+        <v>390.8</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>4630.7</v>
+        <v>390.8</v>
       </c>
       <c r="AG19">
-        <v>3421.9</v>
+        <v>339.9</v>
       </c>
       <c r="AH19">
-        <v>0.9175153556568258</v>
+        <v>0.8891922639362912</v>
       </c>
       <c r="AI19">
-        <v>0.7262589984473267</v>
+        <v>0.8091097308488613</v>
       </c>
       <c r="AJ19">
-        <v>0.8915376999635245</v>
+        <v>0.8746783324755533</v>
       </c>
       <c r="AK19">
-        <v>0.662222050200298</v>
+        <v>0.7866234667900949</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2790,7 +2757,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Bank of Khyber (KASE:BOK)</t>
+          <t>Samba Bank Limited (KASE:SBL)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2799,10 +2766,10 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.0115</v>
+        <v>0.136</v>
       </c>
       <c r="E20">
-        <v>-0.09080000000000001</v>
+        <v>0.0924</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2817,28 +2784,28 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>7.49</v>
+        <v>2.98</v>
       </c>
       <c r="L20">
-        <v>0.1853960396039604</v>
+        <v>0.1354545454545455</v>
       </c>
       <c r="M20">
-        <v>8.800000000000001</v>
+        <v>2.59</v>
       </c>
       <c r="N20">
-        <v>0.0963855421686747</v>
+        <v>0.08961937716262976</v>
       </c>
       <c r="O20">
-        <v>1.174899866488652</v>
+        <v>0.8691275167785234</v>
       </c>
       <c r="P20">
-        <v>8.800000000000001</v>
+        <v>2.59</v>
       </c>
       <c r="Q20">
-        <v>0.0963855421686747</v>
+        <v>0.08961937716262976</v>
       </c>
       <c r="R20">
-        <v>1.174899866488652</v>
+        <v>0.8691275167785234</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -2847,298 +2814,60 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>79</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="V20">
-        <v>0.8652792990142388</v>
+        <v>0.2896193771626298</v>
       </c>
       <c r="W20">
-        <v>0.07146946564885497</v>
+        <v>0.03146779303062302</v>
       </c>
       <c r="X20">
-        <v>0.2887238215895999</v>
+        <v>0.9434061980383039</v>
       </c>
       <c r="Y20">
-        <v>-0.2172543559407449</v>
+        <v>-0.911938405007681</v>
       </c>
       <c r="Z20">
-        <v>0.07480096278466949</v>
+        <v>0.03464566929133858</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.1002375888804264</v>
+        <v>0.1632820168022475</v>
       </c>
       <c r="AC20">
-        <v>-0.1002375888804264</v>
+        <v>-0.1632820168022475</v>
       </c>
       <c r="AD20">
-        <v>442.1</v>
+        <v>399.8</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>442.1</v>
+        <v>399.8</v>
       </c>
       <c r="AG20">
-        <v>363.1</v>
+        <v>391.43</v>
       </c>
       <c r="AH20">
-        <v>0.8288338957630297</v>
+        <v>0.9325868905994869</v>
       </c>
       <c r="AI20">
-        <v>0.8193106004447739</v>
+        <v>0.8570203644158628</v>
       </c>
       <c r="AJ20">
-        <v>0.7990757042253521</v>
+        <v>0.9312444983703281</v>
       </c>
       <c r="AK20">
-        <v>0.7883195831524099</v>
+        <v>0.854408137428241</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Silkbank Limited (KASE:SILK)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>0.0424</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>-6.23</v>
-      </c>
-      <c r="L21">
-        <v>-0.154590570719603</v>
-      </c>
-      <c r="M21">
-        <v>-0</v>
-      </c>
-      <c r="N21">
-        <v>-0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>-0</v>
-      </c>
-      <c r="Q21">
-        <v>-0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>28.5</v>
-      </c>
-      <c r="V21">
-        <v>0.3815261044176707</v>
-      </c>
-      <c r="W21">
-        <v>-0.08306666666666668</v>
-      </c>
-      <c r="X21">
-        <v>0.4852012391387086</v>
-      </c>
-      <c r="Y21">
-        <v>-0.5682679058053752</v>
-      </c>
-      <c r="Z21">
-        <v>0.1175955646337905</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0.1003908201244579</v>
-      </c>
-      <c r="AC21">
-        <v>-0.1003908201244579</v>
-      </c>
-      <c r="AD21">
-        <v>697</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>697</v>
-      </c>
-      <c r="AG21">
-        <v>668.5</v>
-      </c>
-      <c r="AH21">
-        <v>0.9032007256705973</v>
-      </c>
-      <c r="AI21">
-        <v>0.9290855771794188</v>
-      </c>
-      <c r="AJ21">
-        <v>0.8994886975242196</v>
-      </c>
-      <c r="AK21">
-        <v>0.9262851600387972</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Samba Bank Limited (KASE:SBL)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>0.07139999999999999</v>
-      </c>
-      <c r="E22">
-        <v>-0.0159</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>3.32</v>
-      </c>
-      <c r="L22">
-        <v>0.1328</v>
-      </c>
-      <c r="M22">
-        <v>4.34</v>
-      </c>
-      <c r="N22">
-        <v>0.06095505617977528</v>
-      </c>
-      <c r="O22">
-        <v>1.307228915662651</v>
-      </c>
-      <c r="P22">
-        <v>4.34</v>
-      </c>
-      <c r="Q22">
-        <v>0.06095505617977528</v>
-      </c>
-      <c r="R22">
-        <v>1.307228915662651</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>13.8</v>
-      </c>
-      <c r="V22">
-        <v>0.1938202247191011</v>
-      </c>
-      <c r="W22">
-        <v>0.03593073593073592</v>
-      </c>
-      <c r="X22">
-        <v>0.4174225595492931</v>
-      </c>
-      <c r="Y22">
-        <v>-0.3814918236185572</v>
-      </c>
-      <c r="Z22">
-        <v>0.06706008583690988</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>0.1018610721045567</v>
-      </c>
-      <c r="AC22">
-        <v>-0.1018610721045567</v>
-      </c>
-      <c r="AD22">
-        <v>554.1</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>554.1</v>
-      </c>
-      <c r="AG22">
-        <v>540.3000000000001</v>
-      </c>
-      <c r="AH22">
-        <v>0.8861346553654246</v>
-      </c>
-      <c r="AI22">
-        <v>0.8540382244143033</v>
-      </c>
-      <c r="AJ22">
-        <v>0.8835650040883074</v>
-      </c>
-      <c r="AK22">
-        <v>0.8508661417322834</v>
-      </c>
-      <c r="AL22">
-        <v>0</v>
-      </c>
-      <c r="AM22">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/pakistan/pakistan_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_bank_money_center.xlsx
@@ -588,13 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.15</v>
+        <v>0.229</v>
       </c>
       <c r="E2">
-        <v>0.16</v>
-      </c>
-      <c r="F2">
-        <v>0.16</v>
+        <v>0.276</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +600,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-9.675228286499451e-08</v>
+        <v>-7.926625164351433e-08</v>
       </c>
       <c r="J2">
-        <v>-5.465082995306752e-08</v>
+        <v>-4.618246909895479e-08</v>
       </c>
       <c r="K2">
-        <v>1192.27</v>
+        <v>1727.487</v>
       </c>
       <c r="L2">
-        <v>0.2250372775145807</v>
+        <v>0.2836828967895558</v>
       </c>
       <c r="M2">
-        <v>445.347</v>
+        <v>607.7816</v>
       </c>
       <c r="N2">
-        <v>0.09955225215155918</v>
+        <v>0.1055561228920266</v>
       </c>
       <c r="O2">
-        <v>0.3735286470346482</v>
+        <v>0.351829912468227</v>
       </c>
       <c r="P2">
-        <v>445.347</v>
+        <v>586.7816</v>
       </c>
       <c r="Q2">
-        <v>0.09955225215155918</v>
+        <v>0.1019089598638393</v>
       </c>
       <c r="R2">
-        <v>0.3735286470346482</v>
+        <v>0.3396735257631461</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.03455188508503712</v>
       </c>
       <c r="U2">
-        <v>5589.57</v>
+        <v>4709.3</v>
       </c>
       <c r="V2">
-        <v>1.249484743489438</v>
+        <v>0.8178849927925113</v>
       </c>
       <c r="W2">
-        <v>0.1173201312097799</v>
+        <v>0.2063329916433669</v>
       </c>
       <c r="X2">
-        <v>0.5135158795865074</v>
+        <v>0.3516844444855445</v>
       </c>
       <c r="Y2">
-        <v>-0.3961957483767274</v>
+        <v>-0.1453514528421776</v>
       </c>
       <c r="Z2">
-        <v>0.1966180729313421</v>
+        <v>0.2145932395137732</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1539397532465847</v>
+        <v>0.1567947776786013</v>
       </c>
       <c r="AC2">
-        <v>-0.1539397532465847</v>
+        <v>-0.1567947776786013</v>
       </c>
       <c r="AD2">
-        <v>25443.3</v>
+        <v>30755</v>
       </c>
       <c r="AE2">
-        <v>0.002563016349235137</v>
+        <v>0.002413459196915903</v>
       </c>
       <c r="AF2">
-        <v>25443.30256301635</v>
+        <v>30755.00241345919</v>
       </c>
       <c r="AG2">
-        <v>19853.73256301635</v>
+        <v>26045.7024134592</v>
       </c>
       <c r="AH2">
-        <v>0.8504686458194495</v>
+        <v>0.8423050587762216</v>
       </c>
       <c r="AI2">
-        <v>0.7595808701266747</v>
+        <v>0.8021711301197429</v>
       </c>
       <c r="AJ2">
-        <v>0.816111430331748</v>
+        <v>0.8189544717247732</v>
       </c>
       <c r="AK2">
-        <v>0.7114265431424556</v>
+        <v>0.7744689490553186</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank (Pakistan) Limited (KASE:SCBPL)</t>
+          <t>BankIslami Pakistan Limited (KASE:BIPL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.17</v>
+        <v>0.367</v>
       </c>
       <c r="E3">
-        <v>0.16</v>
+        <v>0.4370000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,34 +722,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-2.085448616139249e-06</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>-1.042724308069624e-06</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>79.09999999999999</v>
+        <v>35</v>
       </c>
       <c r="L3">
-        <v>0.3218063466232709</v>
+        <v>0.3111111111111111</v>
       </c>
       <c r="M3">
-        <v>24.9</v>
+        <v>3.51</v>
       </c>
       <c r="N3">
-        <v>0.07351638618246235</v>
+        <v>0.03966101694915254</v>
       </c>
       <c r="O3">
-        <v>0.3147914032869785</v>
+        <v>0.1002857142857143</v>
       </c>
       <c r="P3">
-        <v>24.9</v>
+        <v>3.51</v>
       </c>
       <c r="Q3">
-        <v>0.07351638618246235</v>
+        <v>0.03966101694915254</v>
       </c>
       <c r="R3">
-        <v>0.3147914032869785</v>
+        <v>0.1002857142857143</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>326.4</v>
+        <v>138.3</v>
       </c>
       <c r="V3">
-        <v>0.9636846767050486</v>
+        <v>1.56271186440678</v>
       </c>
       <c r="W3">
-        <v>0.1779527559055118</v>
+        <v>0.3083700440528634</v>
       </c>
       <c r="X3">
-        <v>0.1555066436381044</v>
+        <v>0.136106044565978</v>
       </c>
       <c r="Y3">
-        <v>0.02244611226740739</v>
+        <v>0.1722639994868854</v>
       </c>
       <c r="Z3">
-        <v>1.008606544624277</v>
+        <v>4.97787610619469</v>
       </c>
       <c r="AA3">
-        <v>-1.051698561357844e-06</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1351696099708453</v>
+        <v>0.1296133840871922</v>
       </c>
       <c r="AC3">
-        <v>-0.1351706616694066</v>
+        <v>-0.1296133840871922</v>
       </c>
       <c r="AD3">
-        <v>189</v>
+        <v>35.6</v>
       </c>
       <c r="AE3">
-        <v>0.002563016349235137</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>189.0025630163492</v>
+        <v>35.6</v>
       </c>
       <c r="AG3">
-        <v>-137.3974369836507</v>
+        <v>-102.7</v>
       </c>
       <c r="AH3">
-        <v>0.358161161727186</v>
+        <v>0.2868654311039485</v>
       </c>
       <c r="AI3">
-        <v>0.3447048687436348</v>
+        <v>0.2359178263750828</v>
       </c>
       <c r="AJ3">
-        <v>-0.6825419156361745</v>
+        <v>7.232394366197176</v>
       </c>
       <c r="AK3">
-        <v>-0.6191791348238174</v>
+        <v>-8.150793650793664</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BankIslami Pakistan Limited (KASE:BIPL)</t>
+          <t>Standard Chartered Bank (Pakistan) Limited (KASE:SCBPL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.224</v>
+        <v>0.278</v>
       </c>
       <c r="E4">
-        <v>0.75</v>
+        <v>0.307</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -847,88 +844,91 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>-1.482924237736346e-06</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>-7.414621188681728e-07</v>
       </c>
       <c r="K4">
-        <v>13.7</v>
+        <v>128.8</v>
       </c>
       <c r="L4">
-        <v>0.1802631578947368</v>
+        <v>0.3956989247311828</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>12.7</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.02576064908722109</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.09860248447204968</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>12.7</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.02576064908722109</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.09860248447204968</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>112.8</v>
+        <v>347.5</v>
       </c>
       <c r="V4">
-        <v>1.724770642201835</v>
+        <v>0.704868154158215</v>
       </c>
       <c r="W4">
-        <v>0.1039453717754173</v>
+        <v>0.3584748121347064</v>
       </c>
       <c r="X4">
-        <v>0.1541502225567321</v>
+        <v>0.139156890033647</v>
       </c>
       <c r="Y4">
-        <v>-0.05020485078131477</v>
+        <v>0.2193179221010594</v>
       </c>
       <c r="Z4">
-        <v>2.275449101796407</v>
+        <v>3.022216397437703</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>-2.240858973722295e-06</v>
       </c>
       <c r="AB4">
-        <v>0.1367344547514456</v>
+        <v>0.1310763610967008</v>
       </c>
       <c r="AC4">
-        <v>-0.1367344547514456</v>
+        <v>-0.1310786019556746</v>
       </c>
       <c r="AD4">
-        <v>35</v>
+        <v>226.3</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>0.002413459196915903</v>
       </c>
       <c r="AF4">
-        <v>35</v>
+        <v>226.3024134591969</v>
       </c>
       <c r="AG4">
-        <v>-77.8</v>
+        <v>-121.1975865408031</v>
       </c>
       <c r="AH4">
-        <v>0.348605577689243</v>
+        <v>0.3146137274458543</v>
       </c>
       <c r="AI4">
-        <v>0.2356902356902357</v>
+        <v>0.4098920923770275</v>
       </c>
       <c r="AJ4">
-        <v>6.274193548387101</v>
+        <v>-0.325973103329798</v>
       </c>
       <c r="AK4">
-        <v>-2.179271708683473</v>
+        <v>-0.5923565831493626</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.132</v>
+        <v>0.229</v>
       </c>
       <c r="E5">
-        <v>0.0444</v>
+        <v>0.303</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,28 +972,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>126.7</v>
+        <v>215.4</v>
       </c>
       <c r="L5">
-        <v>0.2532986805277889</v>
+        <v>0.3505859375</v>
       </c>
       <c r="M5">
-        <v>94.2</v>
+        <v>98.7</v>
       </c>
       <c r="N5">
-        <v>0.1548832620848405</v>
+        <v>0.1311279394180949</v>
       </c>
       <c r="O5">
-        <v>0.7434885556432518</v>
+        <v>0.4582172701949861</v>
       </c>
       <c r="P5">
-        <v>94.2</v>
+        <v>98.7</v>
       </c>
       <c r="Q5">
-        <v>0.1548832620848405</v>
+        <v>0.1311279394180949</v>
       </c>
       <c r="R5">
-        <v>0.7434885556432518</v>
+        <v>0.4582172701949861</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1002,55 +1002,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>345</v>
+        <v>232.6</v>
       </c>
       <c r="V5">
-        <v>0.5672476159158171</v>
+        <v>0.3090208582436562</v>
       </c>
       <c r="W5">
-        <v>0.120174523380442</v>
+        <v>0.2857521889095251</v>
       </c>
       <c r="X5">
-        <v>0.2152851501763365</v>
+        <v>0.1952583021789289</v>
       </c>
       <c r="Y5">
-        <v>-0.09511062679589445</v>
+        <v>0.09049388673059619</v>
       </c>
       <c r="Z5">
-        <v>0.2492377619624908</v>
+        <v>0.4516185939842992</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.1441625972485297</v>
+        <v>0.1436701213200354</v>
       </c>
       <c r="AC5">
-        <v>-0.1441625972485297</v>
+        <v>-0.1436701213200354</v>
       </c>
       <c r="AD5">
-        <v>952</v>
+        <v>1131.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>952</v>
+        <v>1131.3</v>
       </c>
       <c r="AG5">
-        <v>607</v>
+        <v>898.6999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.6101781822843225</v>
+        <v>0.6004777070063694</v>
       </c>
       <c r="AI5">
-        <v>0.5570509069631363</v>
+        <v>0.5938894430153814</v>
       </c>
       <c r="AJ5">
-        <v>0.499506254114549</v>
+        <v>0.5442049170400871</v>
       </c>
       <c r="AK5">
-        <v>0.4450146627565982</v>
+        <v>0.5374035759134126</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>United Bank Limited (KASE:UBL)</t>
+          <t>Meezan Bank Limited (KASE:MEBL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,13 +1076,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.08210000000000001</v>
+        <v>0.423</v>
       </c>
       <c r="E6">
-        <v>0.0117</v>
-      </c>
-      <c r="F6">
-        <v>0.16</v>
+        <v>0.551</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1097,28 +1094,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>118.8</v>
+        <v>211.8</v>
       </c>
       <c r="L6">
-        <v>0.22762981414064</v>
+        <v>0.3405692233478052</v>
       </c>
       <c r="M6">
-        <v>88</v>
+        <v>75.2346</v>
       </c>
       <c r="N6">
-        <v>0.1614975224811892</v>
+        <v>0.07205689110238483</v>
       </c>
       <c r="O6">
-        <v>0.7407407407407408</v>
+        <v>0.3552152974504249</v>
       </c>
       <c r="P6">
-        <v>88</v>
+        <v>75.2346</v>
       </c>
       <c r="Q6">
-        <v>0.1614975224811892</v>
+        <v>0.07205689110238483</v>
       </c>
       <c r="R6">
-        <v>0.7407407407407408</v>
+        <v>0.3552152974504249</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1127,55 +1124,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>594.9</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1.091759955955221</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>0.1005416384563304</v>
+        <v>0.4495860751432817</v>
       </c>
       <c r="X6">
-        <v>0.2275797600601449</v>
+        <v>0.2263678664713439</v>
       </c>
       <c r="Y6">
-        <v>-0.1270381216038145</v>
+        <v>0.2232182086719378</v>
       </c>
       <c r="Z6">
-        <v>0.2381582549968057</v>
+        <v>0.2154437746830181</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.1452020057309131</v>
+        <v>0.1473170996593416</v>
       </c>
       <c r="AC6">
-        <v>-0.1452020057309131</v>
+        <v>-0.1473170996593416</v>
       </c>
       <c r="AD6">
-        <v>965.8</v>
+        <v>2173.7</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>965.8</v>
+        <v>2173.7</v>
       </c>
       <c r="AG6">
-        <v>370.9</v>
+        <v>2173.7</v>
       </c>
       <c r="AH6">
-        <v>0.6393062818560933</v>
+        <v>0.6755236496985518</v>
       </c>
       <c r="AI6">
-        <v>0.4967340431003446</v>
+        <v>0.8313382032355529</v>
       </c>
       <c r="AJ6">
-        <v>0.4050010919414719</v>
+        <v>0.6755236496985518</v>
       </c>
       <c r="AK6">
-        <v>0.274862902030532</v>
+        <v>0.8313382032355529</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1192,7 +1189,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meezan Bank Limited (KASE:MEBL)</t>
+          <t>Allied Bank Limited (KASE:ABL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1201,13 +1198,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.331</v>
+        <v>0.214</v>
       </c>
       <c r="E7">
-        <v>0.424</v>
-      </c>
-      <c r="F7">
-        <v>0.3</v>
+        <v>0.234</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1222,28 +1216,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>162.4</v>
+        <v>130.8</v>
       </c>
       <c r="L7">
-        <v>0.3220305373785445</v>
+        <v>0.3106150558062218</v>
       </c>
       <c r="M7">
-        <v>40.8</v>
+        <v>37.7</v>
       </c>
       <c r="N7">
-        <v>0.05184243964421855</v>
+        <v>0.1105571847507331</v>
       </c>
       <c r="O7">
-        <v>0.251231527093596</v>
+        <v>0.2882262996941896</v>
       </c>
       <c r="P7">
-        <v>40.8</v>
+        <v>37.7</v>
       </c>
       <c r="Q7">
-        <v>0.05184243964421855</v>
+        <v>0.1105571847507331</v>
       </c>
       <c r="R7">
-        <v>0.251231527093596</v>
+        <v>0.2882262996941896</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1252,55 +1246,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>392.3</v>
+        <v>176.5</v>
       </c>
       <c r="V7">
-        <v>0.4984752223634054</v>
+        <v>0.5175953079178885</v>
       </c>
       <c r="W7">
-        <v>0.3265634425899859</v>
+        <v>0.2351672060409924</v>
       </c>
       <c r="X7">
-        <v>0.3002374088929327</v>
+        <v>0.2918596481155092</v>
       </c>
       <c r="Y7">
-        <v>0.02632603369705327</v>
+        <v>-0.05669244207451679</v>
       </c>
       <c r="Z7">
-        <v>0.9294139329155916</v>
+        <v>0.2434807747904019</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.149144631459666</v>
+        <v>0.1517855543082118</v>
       </c>
       <c r="AC7">
-        <v>-0.149144631459666</v>
+        <v>-0.1517855543082118</v>
       </c>
       <c r="AD7">
-        <v>2358.4</v>
+        <v>1125.5</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>2358.4</v>
+        <v>1125.5</v>
       </c>
       <c r="AG7">
-        <v>1966.1</v>
+        <v>949</v>
       </c>
       <c r="AH7">
-        <v>0.7497933490176131</v>
+        <v>0.7674735765427889</v>
       </c>
       <c r="AI7">
-        <v>0.838452787258248</v>
+        <v>0.6785843482455083</v>
       </c>
       <c r="AJ7">
-        <v>0.7141404235225745</v>
+        <v>0.7356589147286822</v>
       </c>
       <c r="AK7">
-        <v>0.8122701921090685</v>
+        <v>0.6403076715471291</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1317,7 +1311,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Allied Bank Limited (KASE:ABL)</t>
+          <t>Habib Metropolitan Bank Limited (KASE:HMB)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1326,10 +1320,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.136</v>
+        <v>0.275</v>
       </c>
       <c r="E8">
-        <v>0.06759999999999999</v>
+        <v>0.276</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1344,28 +1338,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>74.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="L8">
-        <v>0.2158231529959279</v>
+        <v>0.3110855389336402</v>
       </c>
       <c r="M8">
-        <v>40</v>
+        <v>34.3</v>
       </c>
       <c r="N8">
-        <v>0.1236093943139678</v>
+        <v>0.1645873320537428</v>
       </c>
       <c r="O8">
-        <v>0.5390835579514824</v>
+        <v>0.4229346485819975</v>
       </c>
       <c r="P8">
-        <v>40</v>
+        <v>34.3</v>
       </c>
       <c r="Q8">
-        <v>0.1236093943139678</v>
+        <v>0.1645873320537428</v>
       </c>
       <c r="R8">
-        <v>0.5390835579514824</v>
+        <v>0.4229346485819975</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1374,55 +1368,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>228.2</v>
+        <v>227.1</v>
       </c>
       <c r="V8">
-        <v>0.7051915945611865</v>
+        <v>1.089731285988484</v>
       </c>
       <c r="W8">
-        <v>0.09618874773139746</v>
+        <v>0.252569293055123</v>
       </c>
       <c r="X8">
-        <v>0.3794237617761525</v>
+        <v>0.3142314749659398</v>
       </c>
       <c r="Y8">
-        <v>-0.283235014044755</v>
+        <v>-0.06166218191081679</v>
       </c>
       <c r="Z8">
-        <v>0.112773076166109</v>
+        <v>0.1790030211480363</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.1513792850600506</v>
+        <v>0.1527828711364135</v>
       </c>
       <c r="AC8">
-        <v>-0.1513792850600506</v>
+        <v>-0.1527828711364135</v>
       </c>
       <c r="AD8">
-        <v>1401.5</v>
+        <v>774.6</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>1401.5</v>
+        <v>774.6</v>
       </c>
       <c r="AG8">
-        <v>1173.3</v>
+        <v>547.5</v>
       </c>
       <c r="AH8">
-        <v>0.8124166714973046</v>
+        <v>0.7879959308240082</v>
       </c>
       <c r="AI8">
-        <v>0.7158910966951014</v>
+        <v>0.7137854773313674</v>
       </c>
       <c r="AJ8">
-        <v>0.7838198944485268</v>
+        <v>0.7243021563698903</v>
       </c>
       <c r="AK8">
-        <v>0.6784041630529054</v>
+        <v>0.6380375247640135</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1439,7 +1433,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Faysal Bank Limited (KASE:FABL)</t>
+          <t>Bank AL Habib Limited (KASE:BAHL)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1448,10 +1442,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.176</v>
+        <v>0.277</v>
       </c>
       <c r="E9">
-        <v>0.179</v>
+        <v>0.307</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1466,28 +1460,28 @@
         <v>0</v>
       </c>
       <c r="K9">
+        <v>108.6</v>
+      </c>
+      <c r="L9">
+        <v>0.2563739376770538</v>
+      </c>
+      <c r="M9">
         <v>43.6</v>
       </c>
-      <c r="L9">
-        <v>0.2259067357512954</v>
-      </c>
-      <c r="M9">
-        <v>4.8</v>
-      </c>
       <c r="N9">
-        <v>0.02771362586605081</v>
+        <v>0.1331297709923664</v>
       </c>
       <c r="O9">
-        <v>0.110091743119266</v>
+        <v>0.4014732965009208</v>
       </c>
       <c r="P9">
-        <v>4.8</v>
+        <v>43.6</v>
       </c>
       <c r="Q9">
-        <v>0.02771362586605081</v>
+        <v>0.1331297709923664</v>
       </c>
       <c r="R9">
-        <v>0.110091743119266</v>
+        <v>0.4014732965009208</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1496,55 +1490,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>142.1</v>
+        <v>172.8</v>
       </c>
       <c r="V9">
-        <v>0.8204387990762125</v>
+        <v>0.5276335877862596</v>
       </c>
       <c r="W9">
-        <v>0.1144657390391179</v>
+        <v>0.2694120565616472</v>
       </c>
       <c r="X9">
-        <v>0.4156347141306339</v>
+        <v>0.3179264852782408</v>
       </c>
       <c r="Y9">
-        <v>-0.301168975091516</v>
+        <v>-0.04851442871659362</v>
       </c>
       <c r="Z9">
-        <v>0.210233239073318</v>
+        <v>0.2115884115884116</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.1520667229734882</v>
+        <v>0.1529308958439269</v>
       </c>
       <c r="AC9">
-        <v>-0.1520667229734882</v>
+        <v>-0.1529308958439269</v>
       </c>
       <c r="AD9">
-        <v>855.8</v>
+        <v>1239.8</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>855.8</v>
+        <v>1239.8</v>
       </c>
       <c r="AG9">
-        <v>713.6999999999999</v>
+        <v>1067</v>
       </c>
       <c r="AH9">
-        <v>0.8316812439261418</v>
+        <v>0.7910419192241435</v>
       </c>
       <c r="AI9">
-        <v>0.7355393210141813</v>
+        <v>0.7505296930806948</v>
       </c>
       <c r="AJ9">
-        <v>0.8047130454391702</v>
+        <v>0.7651487988526353</v>
       </c>
       <c r="AK9">
-        <v>0.6987468180928138</v>
+        <v>0.721384625785951</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1561,7 +1555,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bank AL Habib Limited (KASE:BAHL)</t>
+          <t>Samba Bank Limited (KASE:SBL)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1570,10 +1564,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.211</v>
-      </c>
-      <c r="E10">
-        <v>0.169</v>
+        <v>0.0258</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1588,85 +1579,82 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>85.59999999999999</v>
+        <v>-0.213</v>
       </c>
       <c r="L10">
-        <v>0.2256788821513314</v>
+        <v>-0.01521428571428571</v>
       </c>
       <c r="M10">
-        <v>33.7</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.1241709653647753</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.3936915887850468</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>33.7</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.1241709653647753</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.3936915887850468</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>160.8</v>
+        <v>10.1</v>
       </c>
       <c r="V10">
-        <v>0.5924834193072956</v>
+        <v>0.2589743589743589</v>
       </c>
       <c r="W10">
-        <v>0.1651871864145117</v>
+        <v>-0.002882273342354533</v>
       </c>
       <c r="X10">
-        <v>0.5071899010079906</v>
+        <v>0.2499391525999536</v>
       </c>
       <c r="Y10">
-        <v>-0.3420027145934788</v>
+        <v>-0.2528214259423082</v>
       </c>
       <c r="Z10">
-        <v>0.1555209315675099</v>
+        <v>0.02611453087110614</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.1533048374068057</v>
+        <v>0.1535928091426553</v>
       </c>
       <c r="AC10">
-        <v>-0.1533048374068057</v>
+        <v>-0.1535928091426553</v>
       </c>
       <c r="AD10">
-        <v>1759.7</v>
+        <v>98.3</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>1759.7</v>
+        <v>98.3</v>
       </c>
       <c r="AG10">
-        <v>1598.9</v>
+        <v>88.2</v>
       </c>
       <c r="AH10">
-        <v>0.8663778248239871</v>
+        <v>0.7159504734158776</v>
       </c>
       <c r="AI10">
-        <v>0.8134331807886099</v>
+        <v>0.6557705136757838</v>
       </c>
       <c r="AJ10">
-        <v>0.8548895899053628</v>
+        <v>0.6933962264150944</v>
       </c>
       <c r="AK10">
-        <v>0.7984519350811486</v>
+        <v>0.630901287553648</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1683,7 +1671,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Habib Bank Limited (KASE:HBL)</t>
+          <t>Faysal Bank Limited (KASE:FABL)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1692,13 +1680,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.103</v>
+        <v>0.263</v>
       </c>
       <c r="E11">
-        <v>0.267</v>
-      </c>
-      <c r="F11">
-        <v>0.15</v>
+        <v>0.301</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1713,28 +1698,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>138.8</v>
+        <v>55.4</v>
       </c>
       <c r="L11">
-        <v>0.1666866818782275</v>
+        <v>0.2329688814129521</v>
       </c>
       <c r="M11">
-        <v>43.6</v>
+        <v>43</v>
       </c>
       <c r="N11">
-        <v>0.1055690072639225</v>
+        <v>0.2398215281650864</v>
       </c>
       <c r="O11">
-        <v>0.3141210374639769</v>
+        <v>0.776173285198556</v>
       </c>
       <c r="P11">
-        <v>43.6</v>
+        <v>43</v>
       </c>
       <c r="Q11">
-        <v>0.1055690072639225</v>
+        <v>0.2398215281650864</v>
       </c>
       <c r="R11">
-        <v>0.3141210374639769</v>
+        <v>0.776173285198556</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1743,55 +1728,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>1412.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="V11">
-        <v>3.419370460048426</v>
+        <v>0.532069157836029</v>
       </c>
       <c r="W11">
-        <v>0.08530514412144306</v>
+        <v>0.1800454988625284</v>
       </c>
       <c r="X11">
-        <v>0.5221484635662537</v>
+        <v>0.2713604975324299</v>
       </c>
       <c r="Y11">
-        <v>-0.4368433194448106</v>
+        <v>-0.09131499866990142</v>
       </c>
       <c r="Z11">
-        <v>0.3098879833277511</v>
+        <v>0.2330550001960092</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.1534601933830667</v>
+        <v>0.1551707731862147</v>
       </c>
       <c r="AC11">
-        <v>-0.1534601933830667</v>
+        <v>-0.1551707731862147</v>
       </c>
       <c r="AD11">
-        <v>2781.9</v>
+        <v>523.4</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>2781.9</v>
+        <v>523.4</v>
       </c>
       <c r="AG11">
-        <v>1369.7</v>
+        <v>428</v>
       </c>
       <c r="AH11">
-        <v>0.8707314782935304</v>
+        <v>0.7448413263127934</v>
       </c>
       <c r="AI11">
-        <v>0.6929112284547175</v>
+        <v>0.6544954357884206</v>
       </c>
       <c r="AJ11">
-        <v>0.7683289392494531</v>
+        <v>0.7047587683187881</v>
       </c>
       <c r="AK11">
-        <v>0.5262814108967955</v>
+        <v>0.6076955842680676</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1808,7 +1793,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Habib Metropolitan Bank Limited (KASE:HMB)</t>
+          <t>Askari Bank Limited (KASE:AKBL)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1817,10 +1802,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.187</v>
+        <v>0.204</v>
       </c>
       <c r="E12">
-        <v>0.199</v>
+        <v>0.284</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1835,85 +1820,82 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>60.9</v>
+        <v>58</v>
       </c>
       <c r="L12">
-        <v>0.2923667786845895</v>
+        <v>0.2822384428223844</v>
       </c>
       <c r="M12">
-        <v>25.6</v>
+        <v>-0</v>
       </c>
       <c r="N12">
-        <v>0.1628498727735369</v>
+        <v>-0</v>
       </c>
       <c r="O12">
-        <v>0.4203612479474549</v>
+        <v>-0</v>
       </c>
       <c r="P12">
-        <v>25.6</v>
+        <v>-0</v>
       </c>
       <c r="Q12">
-        <v>0.1628498727735369</v>
+        <v>-0</v>
       </c>
       <c r="R12">
-        <v>0.4203612479474549</v>
+        <v>-0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
-        <v>242.8</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.544529262086514</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>0.1703496503496504</v>
+        <v>0.1819322459222083</v>
       </c>
       <c r="X12">
-        <v>0.6426670326298241</v>
+        <v>0.6203534547275067</v>
       </c>
       <c r="Y12">
-        <v>-0.4723173822801737</v>
+        <v>-0.4384212088052984</v>
       </c>
       <c r="Z12">
-        <v>0.1154656319290466</v>
+        <v>0.1175562038784967</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.1544193131101026</v>
+        <v>0.158418782170988</v>
       </c>
       <c r="AC12">
-        <v>-0.1544193131101026</v>
+        <v>-0.158418782170988</v>
       </c>
       <c r="AD12">
-        <v>1378.1</v>
+        <v>1200.2</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>1378.1</v>
+        <v>1200.2</v>
       </c>
       <c r="AG12">
-        <v>1135.3</v>
+        <v>1200.2</v>
       </c>
       <c r="AH12">
-        <v>0.897609587702729</v>
+        <v>0.9039692701664532</v>
       </c>
       <c r="AI12">
-        <v>0.8035568513119533</v>
+        <v>0.8269257268843875</v>
       </c>
       <c r="AJ12">
-        <v>0.8783752417794971</v>
+        <v>0.9039692701664532</v>
       </c>
       <c r="AK12">
-        <v>0.7711588099443011</v>
+        <v>0.8269257268843875</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1930,7 +1912,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Bank of Punjab (KASE:BOP)</t>
+          <t>Habib Bank Limited (KASE:HBL)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1939,10 +1921,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.209</v>
+        <v>0.207</v>
       </c>
       <c r="E13">
-        <v>0.226</v>
+        <v>0.26</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1957,28 +1939,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>49</v>
+        <v>186</v>
       </c>
       <c r="L13">
-        <v>0.2494908350305499</v>
+        <v>0.2024159320927196</v>
       </c>
       <c r="M13">
-        <v>14.871</v>
+        <v>41.6</v>
       </c>
       <c r="N13">
-        <v>0.24785</v>
+        <v>0.06908003985386914</v>
       </c>
       <c r="O13">
-        <v>0.3034897959183673</v>
+        <v>0.2236559139784946</v>
       </c>
       <c r="P13">
-        <v>14.871</v>
+        <v>41.6</v>
       </c>
       <c r="Q13">
-        <v>0.24785</v>
+        <v>0.06908003985386914</v>
       </c>
       <c r="R13">
-        <v>0.3034897959183673</v>
+        <v>0.2236559139784946</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1987,55 +1969,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>135.5</v>
+        <v>1230.3</v>
       </c>
       <c r="V13">
-        <v>2.258333333333333</v>
+        <v>2.043008967120558</v>
       </c>
       <c r="W13">
-        <v>0.1574550128534704</v>
+        <v>0.1523840734065214</v>
       </c>
       <c r="X13">
-        <v>0.7381262214407531</v>
+        <v>0.3854424036928482</v>
       </c>
       <c r="Y13">
-        <v>-0.5806712085872827</v>
+        <v>-0.2330583302863268</v>
       </c>
       <c r="Z13">
-        <v>0.2156346069389548</v>
+        <v>0.3547465544531521</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.1549359583220422</v>
+        <v>0.1584859827940118</v>
       </c>
       <c r="AC13">
-        <v>-0.1549359583220422</v>
+        <v>-0.1584859827940118</v>
       </c>
       <c r="AD13">
-        <v>622.5</v>
+        <v>3036.3</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>622.5</v>
+        <v>3036.3</v>
       </c>
       <c r="AG13">
-        <v>487</v>
+        <v>1806</v>
       </c>
       <c r="AH13">
-        <v>0.9120879120879121</v>
+        <v>0.8344922358114608</v>
       </c>
       <c r="AI13">
-        <v>0.6880733944954128</v>
+        <v>0.7192807902778765</v>
       </c>
       <c r="AJ13">
-        <v>0.8903107861060329</v>
+        <v>0.7499377128145504</v>
       </c>
       <c r="AK13">
-        <v>0.6331253250130005</v>
+        <v>0.6038114343029088</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2052,7 +2034,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bank Alfalah Limited (KASE:BAFL)</t>
+          <t>The Bank of Khyber (KASE:BOK)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2061,10 +2043,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.152</v>
+        <v>0.164</v>
       </c>
       <c r="E14">
-        <v>0.154</v>
+        <v>0.145</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2079,28 +2061,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>78.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L14">
-        <v>0.2247575584711922</v>
+        <v>0.2017543859649123</v>
       </c>
       <c r="M14">
-        <v>25</v>
+        <v>0.001</v>
       </c>
       <c r="N14">
-        <v>0.1056635672020287</v>
+        <v>1.941747572815534e-05</v>
       </c>
       <c r="O14">
-        <v>0.317258883248731</v>
+        <v>0.000108695652173913</v>
       </c>
       <c r="P14">
-        <v>25</v>
+        <v>0.001</v>
       </c>
       <c r="Q14">
-        <v>0.1056635672020287</v>
+        <v>1.941747572815534e-05</v>
       </c>
       <c r="R14">
-        <v>0.317258883248731</v>
+        <v>0.000108695652173913</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2109,55 +2091,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>176.3</v>
+        <v>38.8</v>
       </c>
       <c r="V14">
-        <v>0.7451394759087068</v>
+        <v>0.7533980582524271</v>
       </c>
       <c r="W14">
-        <v>0.1425728243169893</v>
+        <v>0.1265474552957359</v>
       </c>
       <c r="X14">
-        <v>0.7441149683980643</v>
+        <v>0.3989412081735201</v>
       </c>
       <c r="Y14">
-        <v>-0.6015421440810751</v>
+        <v>-0.2723937528777842</v>
       </c>
       <c r="Z14">
-        <v>0.1403017327624155</v>
+        <v>0.1313742437337943</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.1549635427674074</v>
+        <v>0.1604281549407502</v>
       </c>
       <c r="AC14">
-        <v>-0.1549635427674074</v>
+        <v>-0.1604281549407502</v>
       </c>
       <c r="AD14">
-        <v>2478.6</v>
+        <v>272.6</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>2478.6</v>
+        <v>272.6</v>
       </c>
       <c r="AG14">
-        <v>2302.3</v>
+        <v>233.8</v>
       </c>
       <c r="AH14">
-        <v>0.9128609310548026</v>
+        <v>0.8410984264116014</v>
       </c>
       <c r="AI14">
-        <v>0.8431472599244821</v>
+        <v>0.8120345546619004</v>
       </c>
       <c r="AJ14">
-        <v>0.9068100358422939</v>
+        <v>0.8194882579740624</v>
       </c>
       <c r="AK14">
-        <v>0.8331403343707028</v>
+        <v>0.7874705287975748</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2174,7 +2156,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Askari Bank Limited (KASE:AKBL)</t>
+          <t>Bank Makramah Limited (KASE:BML)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2182,104 +2164,80 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D15">
-        <v>0.15</v>
-      </c>
-      <c r="E15">
-        <v>0.218</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
       <c r="K15">
-        <v>59.8</v>
-      </c>
-      <c r="L15">
-        <v>0.2861244019138756</v>
+        <v>-17.2</v>
       </c>
       <c r="M15">
-        <v>0.042</v>
+        <v>-0</v>
       </c>
       <c r="N15">
-        <v>0.0003753351206434316</v>
+        <v>-0</v>
       </c>
       <c r="O15">
-        <v>0.0007023411371237459</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>0.042</v>
+        <v>-0</v>
       </c>
       <c r="Q15">
-        <v>0.0003753351206434316</v>
+        <v>-0</v>
       </c>
       <c r="R15">
-        <v>0.0007023411371237459</v>
+        <v>0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
       <c r="U15">
-        <v>180.4</v>
+        <v>19.3</v>
       </c>
       <c r="V15">
-        <v>1.612153708668454</v>
+        <v>0.3464991023339318</v>
       </c>
       <c r="W15">
-        <v>0.182205971968312</v>
+        <v>0.2365887207702888</v>
       </c>
       <c r="X15">
-        <v>0.8979459606343869</v>
+        <v>0.5314738564475954</v>
       </c>
       <c r="Y15">
-        <v>-0.7157399886660749</v>
+        <v>-0.2948851356773066</v>
       </c>
       <c r="Z15">
-        <v>0.3182579564489113</v>
+        <v>0</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.1555364624175127</v>
+        <v>0.1611930532228295</v>
       </c>
       <c r="AC15">
-        <v>-0.1555364624175127</v>
+        <v>-0.1611930532228295</v>
       </c>
       <c r="AD15">
-        <v>1462.3</v>
+        <v>432.2</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>1462.3</v>
+        <v>432.2</v>
       </c>
       <c r="AG15">
-        <v>1281.9</v>
+        <v>412.9</v>
       </c>
       <c r="AH15">
-        <v>0.9289162749332994</v>
+        <v>0.8858372617339619</v>
       </c>
       <c r="AI15">
-        <v>0.8322235501678903</v>
+        <v>1.101707876625032</v>
       </c>
       <c r="AJ15">
-        <v>0.9197158846319414</v>
+        <v>0.8811352966282544</v>
       </c>
       <c r="AK15">
-        <v>0.8130272087270882</v>
+        <v>1.106970509383378</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2296,7 +2254,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>National Bank of Pakistan (KASE:NBP)</t>
+          <t>United Bank Limited (KASE:UBL)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2305,10 +2263,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.0906</v>
+        <v>0.175</v>
       </c>
       <c r="E16">
-        <v>-0.007189999999999999</v>
+        <v>0.273</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2323,28 +2281,28 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>101.9</v>
+        <v>190.3</v>
       </c>
       <c r="L16">
-        <v>0.1660691003911343</v>
+        <v>0.3252991452991453</v>
       </c>
       <c r="M16">
-        <v>0.004</v>
+        <v>168</v>
       </c>
       <c r="N16">
-        <v>1.804239963915201e-05</v>
+        <v>0.2099212795201799</v>
       </c>
       <c r="O16">
-        <v>3.925417075564279e-05</v>
+        <v>0.8828166053599579</v>
       </c>
       <c r="P16">
-        <v>0.004</v>
+        <v>168</v>
       </c>
       <c r="Q16">
-        <v>1.804239963915201e-05</v>
+        <v>0.2099212795201799</v>
       </c>
       <c r="R16">
-        <v>3.925417075564279e-05</v>
+        <v>0.8828166053599579</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2353,55 +2311,55 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>997.1</v>
+        <v>827</v>
       </c>
       <c r="V16">
-        <v>4.497519170049617</v>
+        <v>1.0333624890666</v>
       </c>
       <c r="W16">
-        <v>0.05858341956996665</v>
+        <v>0.2016744383213226</v>
       </c>
       <c r="X16">
-        <v>1.983464022605</v>
+        <v>0.438602548187989</v>
       </c>
       <c r="Y16">
-        <v>-1.924880603035034</v>
+        <v>-0.2369281098666664</v>
       </c>
       <c r="Z16">
-        <v>0.1189608375339279</v>
+        <v>0.4450361354127044</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.1569702485975942</v>
+        <v>0.1613391367979939</v>
       </c>
       <c r="AC16">
-        <v>-0.1569702485975942</v>
+        <v>-0.1613391367979939</v>
       </c>
       <c r="AD16">
-        <v>6952.2</v>
+        <v>4826.8</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>6952.2</v>
+        <v>4826.8</v>
       </c>
       <c r="AG16">
-        <v>5955.099999999999</v>
+        <v>3999.8</v>
       </c>
       <c r="AH16">
-        <v>0.9690963074478317</v>
+        <v>0.8577775408292015</v>
       </c>
       <c r="AI16">
-        <v>0.8367676086851861</v>
+        <v>0.8467921615410255</v>
       </c>
       <c r="AJ16">
-        <v>0.9641076285455252</v>
+        <v>0.8332743067852753</v>
       </c>
       <c r="AK16">
-        <v>0.8145063121469506</v>
+        <v>0.8207916931727237</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2418,7 +2376,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Bank of Khyber (KASE:BOK)</t>
+          <t>Soneri Bank Limited (KASE:SNBL)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2427,10 +2385,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.0147</v>
+        <v>0.186</v>
       </c>
       <c r="E17">
-        <v>-0.207</v>
+        <v>0.224</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2445,82 +2403,85 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>2.65</v>
+        <v>16.5</v>
       </c>
       <c r="L17">
-        <v>0.08466453674121405</v>
+        <v>0.1987951807228916</v>
       </c>
       <c r="M17">
-        <v>-0</v>
+        <v>3.81</v>
       </c>
       <c r="N17">
-        <v>-0</v>
+        <v>0.09114832535885169</v>
       </c>
       <c r="O17">
-        <v>-0</v>
+        <v>0.2309090909090909</v>
       </c>
       <c r="P17">
-        <v>-0</v>
+        <v>3.81</v>
       </c>
       <c r="Q17">
-        <v>-0</v>
+        <v>0.09114832535885169</v>
       </c>
       <c r="R17">
-        <v>-0</v>
+        <v>0.2309090909090909</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
       <c r="U17">
-        <v>52.9</v>
+        <v>40.2</v>
       </c>
       <c r="V17">
-        <v>0.8357030015797788</v>
+        <v>0.9617224880382776</v>
       </c>
       <c r="W17">
-        <v>0.02717948717948718</v>
+        <v>0.1789587852494577</v>
       </c>
       <c r="X17">
-        <v>0.4292555680592771</v>
+        <v>0.4609650271493006</v>
       </c>
       <c r="Y17">
-        <v>-0.40207608087979</v>
+        <v>-0.2820062418998429</v>
       </c>
       <c r="Z17">
-        <v>0.06795484151107251</v>
+        <v>0.1920851654709558</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.1591319122189949</v>
+        <v>0.1617731782948338</v>
       </c>
       <c r="AC17">
-        <v>-0.1591319122189949</v>
+        <v>-0.1617731782948338</v>
       </c>
       <c r="AD17">
-        <v>327.3</v>
+        <v>269.5</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>327.3</v>
+        <v>269.5</v>
       </c>
       <c r="AG17">
-        <v>274.4</v>
+        <v>229.3</v>
       </c>
       <c r="AH17">
-        <v>0.8379416282642089</v>
+        <v>0.8657243816254416</v>
       </c>
       <c r="AI17">
-        <v>0.81825</v>
+        <v>0.756385068762279</v>
       </c>
       <c r="AJ17">
-        <v>0.8125555226532425</v>
+        <v>0.8458133530062707</v>
       </c>
       <c r="AK17">
-        <v>0.7905502736963411</v>
+        <v>0.7254033533691869</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2537,7 +2498,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Summit Bank Limited (KASE:SMBL)</t>
+          <t>National Bank of Pakistan (KASE:NBP)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2545,80 +2506,104 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D18">
+        <v>0.153</v>
+      </c>
+      <c r="E18">
+        <v>0.157</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
       <c r="K18">
-        <v>-14.5</v>
+        <v>177.1</v>
+      </c>
+      <c r="L18">
+        <v>0.2886715566422168</v>
       </c>
       <c r="M18">
-        <v>-0</v>
+        <v>0.026</v>
       </c>
       <c r="N18">
-        <v>-0</v>
+        <v>0.0001041249499399279</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>0.0001468097120271033</v>
       </c>
       <c r="P18">
-        <v>-0</v>
+        <v>0.026</v>
       </c>
       <c r="Q18">
-        <v>-0</v>
+        <v>0.0001041249499399279</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>0.0001468097120271033</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
       <c r="U18">
-        <v>30.6</v>
+        <v>887.8</v>
       </c>
       <c r="V18">
-        <v>1.545454545454545</v>
+        <v>3.555466559871846</v>
       </c>
       <c r="W18">
-        <v>0.1892950391644909</v>
+        <v>0.131039585645579</v>
       </c>
       <c r="X18">
-        <v>0.5198418581650242</v>
+        <v>2.082800916819151</v>
       </c>
       <c r="Y18">
-        <v>-0.3305468190005333</v>
+        <v>-1.951761331173572</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>0.08399346124252821</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.1605410939579424</v>
+        <v>0.1617940196700479</v>
       </c>
       <c r="AC18">
-        <v>-0.1605410939579424</v>
+        <v>-0.1617940196700479</v>
       </c>
       <c r="AD18">
-        <v>132.6</v>
+        <v>9145.799999999999</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>132.6</v>
+        <v>9145.799999999999</v>
       </c>
       <c r="AG18">
-        <v>102</v>
+        <v>8258</v>
       </c>
       <c r="AH18">
-        <v>0.8700787401574802</v>
+        <v>0.9734234473950295</v>
       </c>
       <c r="AI18">
-        <v>2.213689482470785</v>
+        <v>0.8801062386327551</v>
       </c>
       <c r="AJ18">
-        <v>0.8374384236453202</v>
+        <v>0.970650116952878</v>
       </c>
       <c r="AK18">
-        <v>3.48122866894198</v>
+        <v>0.8689064489314913</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2635,7 +2620,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Soneri Bank Limited (KASE:SNBL)</t>
+          <t>Bank Alfalah Limited (KASE:BAFL)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2644,10 +2629,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.111</v>
+        <v>0.247</v>
       </c>
       <c r="E19">
-        <v>0.0269</v>
+        <v>0.257</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2662,85 +2647,85 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>7.84</v>
+        <v>109.8</v>
       </c>
       <c r="L19">
-        <v>0.1121602288984263</v>
+        <v>0.2532287822878229</v>
       </c>
       <c r="M19">
-        <v>7.24</v>
+        <v>45.6</v>
       </c>
       <c r="N19">
-        <v>0.1486652977412731</v>
+        <v>0.1656976744186047</v>
       </c>
       <c r="O19">
-        <v>0.9234693877551021</v>
+        <v>0.4153005464480874</v>
       </c>
       <c r="P19">
-        <v>7.24</v>
+        <v>24.6</v>
       </c>
       <c r="Q19">
-        <v>0.1486652977412731</v>
+        <v>0.08938953488372094</v>
       </c>
       <c r="R19">
-        <v>0.9234693877551021</v>
+        <v>0.2240437158469946</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>0.4605263157894737</v>
       </c>
       <c r="U19">
-        <v>50.9</v>
+        <v>160.9</v>
       </c>
       <c r="V19">
-        <v>1.04517453798768</v>
+        <v>0.5846656976744187</v>
       </c>
       <c r="W19">
-        <v>0.05872659176029962</v>
+        <v>0.2109915449654112</v>
       </c>
       <c r="X19">
-        <v>0.5986366984167468</v>
+        <v>0.4869527891211656</v>
       </c>
       <c r="Y19">
-        <v>-0.5399101066564472</v>
+        <v>-0.2759612441557544</v>
       </c>
       <c r="Z19">
-        <v>0.1023126463700234</v>
+        <v>0.1592127487699199</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.1613792037658644</v>
+        <v>0.1622203623220549</v>
       </c>
       <c r="AC19">
-        <v>-0.1613792037658644</v>
+        <v>-0.1622203623220549</v>
       </c>
       <c r="AD19">
-        <v>390.8</v>
+        <v>1907.4</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>390.8</v>
+        <v>1907.4</v>
       </c>
       <c r="AG19">
-        <v>339.9</v>
+        <v>1746.5</v>
       </c>
       <c r="AH19">
-        <v>0.8891922639362912</v>
+        <v>0.8739118482543756</v>
       </c>
       <c r="AI19">
-        <v>0.8091097308488613</v>
+        <v>0.8181350261645364</v>
       </c>
       <c r="AJ19">
-        <v>0.8746783324755533</v>
+        <v>0.8638769352525102</v>
       </c>
       <c r="AK19">
-        <v>0.7866234667900949</v>
+        <v>0.8046533056899332</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2757,7 +2742,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Samba Bank Limited (KASE:SBL)</t>
+          <t>The Bank of Punjab (KASE:BOP)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2766,10 +2751,7 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.136</v>
-      </c>
-      <c r="E20">
-        <v>0.0924</v>
+        <v>0.364</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2784,85 +2766,82 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>2.98</v>
+        <v>31.1</v>
       </c>
       <c r="L20">
-        <v>0.1354545454545455</v>
+        <v>0.1798727588201272</v>
       </c>
       <c r="M20">
-        <v>2.59</v>
+        <v>-0</v>
       </c>
       <c r="N20">
-        <v>0.08961937716262976</v>
+        <v>-0</v>
       </c>
       <c r="O20">
-        <v>0.8691275167785234</v>
+        <v>-0</v>
       </c>
       <c r="P20">
-        <v>2.59</v>
+        <v>-0</v>
       </c>
       <c r="Q20">
-        <v>0.08961937716262976</v>
+        <v>-0</v>
       </c>
       <c r="R20">
-        <v>0.8691275167785234</v>
+        <v>-0</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
       <c r="U20">
-        <v>8.369999999999999</v>
+        <v>104.7</v>
       </c>
       <c r="V20">
-        <v>0.2896193771626298</v>
+        <v>1.300621118012422</v>
       </c>
       <c r="W20">
-        <v>0.03146779303062302</v>
+        <v>0.1113498030791264</v>
       </c>
       <c r="X20">
-        <v>0.9434061980383039</v>
+        <v>1.673725315305657</v>
       </c>
       <c r="Y20">
-        <v>-0.911938405007681</v>
+        <v>-1.56237551222653</v>
       </c>
       <c r="Z20">
-        <v>0.03464566929133858</v>
+        <v>0.2256296489625473</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.1632820168022475</v>
+        <v>0.1654555051989869</v>
       </c>
       <c r="AC20">
-        <v>-0.1632820168022475</v>
+        <v>-0.1654555051989869</v>
       </c>
       <c r="AD20">
-        <v>399.8</v>
+        <v>2335.7</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>399.8</v>
+        <v>2335.7</v>
       </c>
       <c r="AG20">
-        <v>391.43</v>
+        <v>2231</v>
       </c>
       <c r="AH20">
-        <v>0.9325868905994869</v>
+        <v>0.9666832215876169</v>
       </c>
       <c r="AI20">
-        <v>0.8570203644158628</v>
+        <v>0.9012579101713227</v>
       </c>
       <c r="AJ20">
-        <v>0.9312444983703281</v>
+        <v>0.9651741293532339</v>
       </c>
       <c r="AK20">
-        <v>0.854408137428241</v>
+        <v>0.8971008082351521</v>
       </c>
       <c r="AL20">
         <v>0</v>
